--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -112,8 +118,13 @@
         <fgColor rgb="008B1E22"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B08F36"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -179,11 +190,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -378,6 +403,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -624,13 +655,13 @@
 (직접 입력)</t>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <t>▣ 상태
 (직접 입력)</t>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0" shapeId="0">
       <text>
         <t>▣ 메모
 (직접 입력)</t>
@@ -930,7 +961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -951,7 +982,7 @@
     <col width="6" customWidth="1" style="55" min="16" max="16"/>
     <col width="8" customWidth="1" style="55" min="17" max="17"/>
     <col width="9" customWidth="1" style="55" min="18" max="18"/>
-    <col width="10" customWidth="1" style="55" min="19" max="19"/>
+    <col width="12" customWidth="1" style="55" min="19" max="19"/>
     <col width="28" customWidth="1" style="55" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -978,8 +1009,8 @@
       <c r="P1" s="16" t="n"/>
       <c r="Q1" s="16" t="n"/>
       <c r="R1" s="16" t="n"/>
-      <c r="S1" s="16" t="n"/>
-      <c r="T1" s="17" t="n"/>
+      <c r="T1" s="16" t="n"/>
+      <c r="U1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="63" t="inlineStr">
@@ -1004,8 +1035,8 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="16" t="n"/>
-      <c r="S2" s="17" t="n"/>
-      <c r="T2" s="64" t="inlineStr">
+      <c r="T2" s="17" t="n"/>
+      <c r="U2" s="64" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -1102,12 +1133,17 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S3" s="65" t="inlineStr">
+        <is>
+          <t>✏입력</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1204,12 +1240,18 @@
           <t>AUTORUN</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="66" t="inlineStr">
+        <is>
+          <t>가공
+입고일</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="T4" s="7" t="inlineStr">
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1270,8 +1312,8 @@
       <c r="P5" s="11" t="n"/>
       <c r="Q5" s="11" t="n"/>
       <c r="R5" s="11" t="n"/>
-      <c r="S5" s="9" t="n"/>
-      <c r="T5" s="22" t="n"/>
+      <c r="T5" s="9" t="n"/>
+      <c r="U5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1328,8 +1370,8 @@
       <c r="P6" s="15" t="n"/>
       <c r="Q6" s="15" t="n"/>
       <c r="R6" s="15" t="n"/>
-      <c r="S6" s="13" t="n"/>
-      <c r="T6" s="24" t="n"/>
+      <c r="T6" s="13" t="n"/>
+      <c r="U6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1384,8 +1426,8 @@
       <c r="P7" s="11" t="n"/>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="11" t="n"/>
-      <c r="S7" s="9" t="n"/>
-      <c r="T7" s="22" t="n"/>
+      <c r="T7" s="9" t="n"/>
+      <c r="U7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1440,8 +1482,8 @@
       <c r="P8" s="15" t="n"/>
       <c r="Q8" s="15" t="n"/>
       <c r="R8" s="15" t="n"/>
-      <c r="S8" s="13" t="n"/>
-      <c r="T8" s="24" t="n"/>
+      <c r="T8" s="13" t="n"/>
+      <c r="U8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1496,8 +1538,8 @@
       <c r="P9" s="11" t="n"/>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="11" t="n"/>
-      <c r="S9" s="9" t="n"/>
-      <c r="T9" s="22" t="n"/>
+      <c r="T9" s="9" t="n"/>
+      <c r="U9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1552,8 +1594,8 @@
       <c r="P10" s="15" t="n"/>
       <c r="Q10" s="15" t="n"/>
       <c r="R10" s="15" t="n"/>
-      <c r="S10" s="13" t="n"/>
-      <c r="T10" s="24" t="n"/>
+      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1608,8 +1650,8 @@
       <c r="P11" s="11" t="n"/>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="11" t="n"/>
-      <c r="S11" s="9" t="n"/>
-      <c r="T11" s="22" t="n"/>
+      <c r="T11" s="9" t="n"/>
+      <c r="U11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -1664,8 +1706,8 @@
       <c r="P12" s="15" t="n"/>
       <c r="Q12" s="15" t="n"/>
       <c r="R12" s="15" t="n"/>
-      <c r="S12" s="13" t="n"/>
-      <c r="T12" s="24" t="n"/>
+      <c r="T12" s="13" t="n"/>
+      <c r="U12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -1720,8 +1762,8 @@
       <c r="P13" s="11" t="n"/>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="11" t="n"/>
-      <c r="S13" s="9" t="n"/>
-      <c r="T13" s="22" t="n"/>
+      <c r="T13" s="9" t="n"/>
+      <c r="U13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -1776,8 +1818,8 @@
       <c r="P14" s="15" t="n"/>
       <c r="Q14" s="15" t="n"/>
       <c r="R14" s="15" t="n"/>
-      <c r="S14" s="13" t="n"/>
-      <c r="T14" s="24" t="n"/>
+      <c r="T14" s="13" t="n"/>
+      <c r="U14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -1832,8 +1874,8 @@
       <c r="P15" s="11" t="n"/>
       <c r="Q15" s="11" t="n"/>
       <c r="R15" s="11" t="n"/>
-      <c r="S15" s="9" t="n"/>
-      <c r="T15" s="22" t="n"/>
+      <c r="T15" s="9" t="n"/>
+      <c r="U15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -1890,8 +1932,8 @@
       <c r="P16" s="15" t="n"/>
       <c r="Q16" s="15" t="n"/>
       <c r="R16" s="15" t="n"/>
-      <c r="S16" s="13" t="n"/>
-      <c r="T16" s="24" t="n"/>
+      <c r="T16" s="13" t="n"/>
+      <c r="U16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -1948,8 +1990,8 @@
       <c r="P17" s="11" t="n"/>
       <c r="Q17" s="11" t="n"/>
       <c r="R17" s="11" t="n"/>
-      <c r="S17" s="9" t="n"/>
-      <c r="T17" s="22" t="n"/>
+      <c r="T17" s="9" t="n"/>
+      <c r="U17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -2004,8 +2046,8 @@
       <c r="P18" s="15" t="n"/>
       <c r="Q18" s="15" t="n"/>
       <c r="R18" s="15" t="n"/>
-      <c r="S18" s="13" t="n"/>
-      <c r="T18" s="24" t="n"/>
+      <c r="T18" s="13" t="n"/>
+      <c r="U18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2060,8 +2102,8 @@
       <c r="P19" s="11" t="n"/>
       <c r="Q19" s="11" t="n"/>
       <c r="R19" s="11" t="n"/>
-      <c r="S19" s="9" t="n"/>
-      <c r="T19" s="22" t="n"/>
+      <c r="T19" s="9" t="n"/>
+      <c r="U19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2116,8 +2158,8 @@
       <c r="P20" s="15" t="n"/>
       <c r="Q20" s="15" t="n"/>
       <c r="R20" s="15" t="n"/>
-      <c r="S20" s="13" t="n"/>
-      <c r="T20" s="24" t="n"/>
+      <c r="T20" s="13" t="n"/>
+      <c r="U20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2172,8 +2214,8 @@
       <c r="P21" s="11" t="n"/>
       <c r="Q21" s="11" t="n"/>
       <c r="R21" s="11" t="n"/>
-      <c r="S21" s="9" t="n"/>
-      <c r="T21" s="22" t="n"/>
+      <c r="T21" s="9" t="n"/>
+      <c r="U21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2228,8 +2270,8 @@
       <c r="P22" s="15" t="n"/>
       <c r="Q22" s="15" t="n"/>
       <c r="R22" s="15" t="n"/>
-      <c r="S22" s="13" t="n"/>
-      <c r="T22" s="24" t="n"/>
+      <c r="T22" s="13" t="n"/>
+      <c r="U22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2284,8 +2326,8 @@
       <c r="P23" s="11" t="n"/>
       <c r="Q23" s="11" t="n"/>
       <c r="R23" s="11" t="n"/>
-      <c r="S23" s="9" t="n"/>
-      <c r="T23" s="22" t="n"/>
+      <c r="T23" s="9" t="n"/>
+      <c r="U23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2340,8 +2382,8 @@
       <c r="P24" s="15" t="n"/>
       <c r="Q24" s="15" t="n"/>
       <c r="R24" s="15" t="n"/>
-      <c r="S24" s="13" t="n"/>
-      <c r="T24" s="24" t="n"/>
+      <c r="T24" s="13" t="n"/>
+      <c r="U24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2396,8 +2438,8 @@
       <c r="P25" s="11" t="n"/>
       <c r="Q25" s="11" t="n"/>
       <c r="R25" s="11" t="n"/>
-      <c r="S25" s="9" t="n"/>
-      <c r="T25" s="22" t="n"/>
+      <c r="T25" s="9" t="n"/>
+      <c r="U25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2452,8 +2494,8 @@
       <c r="P26" s="15" t="n"/>
       <c r="Q26" s="15" t="n"/>
       <c r="R26" s="15" t="n"/>
-      <c r="S26" s="13" t="n"/>
-      <c r="T26" s="24" t="n"/>
+      <c r="T26" s="13" t="n"/>
+      <c r="U26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -2508,8 +2550,8 @@
       <c r="P27" s="11" t="n"/>
       <c r="Q27" s="11" t="n"/>
       <c r="R27" s="11" t="n"/>
-      <c r="S27" s="9" t="n"/>
-      <c r="T27" s="22" t="n"/>
+      <c r="T27" s="9" t="n"/>
+      <c r="U27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n"/>
@@ -2530,8 +2572,8 @@
       <c r="P28" s="13" t="n"/>
       <c r="Q28" s="13" t="n"/>
       <c r="R28" s="13" t="n"/>
-      <c r="S28" s="13" t="n"/>
-      <c r="T28" s="24" t="n"/>
+      <c r="T28" s="13" t="n"/>
+      <c r="U28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n"/>
@@ -2552,8 +2594,8 @@
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
-      <c r="S29" s="9" t="n"/>
-      <c r="T29" s="22" t="n"/>
+      <c r="T29" s="9" t="n"/>
+      <c r="U29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n"/>
@@ -2574,8 +2616,8 @@
       <c r="P30" s="13" t="n"/>
       <c r="Q30" s="13" t="n"/>
       <c r="R30" s="13" t="n"/>
-      <c r="S30" s="13" t="n"/>
-      <c r="T30" s="24" t="n"/>
+      <c r="T30" s="13" t="n"/>
+      <c r="U30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n"/>
@@ -2596,8 +2638,8 @@
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n"/>
       <c r="R31" s="9" t="n"/>
-      <c r="S31" s="9" t="n"/>
-      <c r="T31" s="22" t="n"/>
+      <c r="T31" s="9" t="n"/>
+      <c r="U31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n"/>
@@ -2618,8 +2660,8 @@
       <c r="P32" s="13" t="n"/>
       <c r="Q32" s="13" t="n"/>
       <c r="R32" s="13" t="n"/>
-      <c r="S32" s="13" t="n"/>
-      <c r="T32" s="24" t="n"/>
+      <c r="T32" s="13" t="n"/>
+      <c r="U32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n"/>
@@ -2640,8 +2682,8 @@
       <c r="P33" s="9" t="n"/>
       <c r="Q33" s="9" t="n"/>
       <c r="R33" s="9" t="n"/>
-      <c r="S33" s="9" t="n"/>
-      <c r="T33" s="22" t="n"/>
+      <c r="T33" s="9" t="n"/>
+      <c r="U33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n"/>
@@ -2662,8 +2704,8 @@
       <c r="P34" s="13" t="n"/>
       <c r="Q34" s="13" t="n"/>
       <c r="R34" s="13" t="n"/>
-      <c r="S34" s="13" t="n"/>
-      <c r="T34" s="24" t="n"/>
+      <c r="T34" s="13" t="n"/>
+      <c r="U34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n"/>
@@ -2684,8 +2726,8 @@
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
       <c r="R35" s="9" t="n"/>
-      <c r="S35" s="9" t="n"/>
-      <c r="T35" s="22" t="n"/>
+      <c r="T35" s="9" t="n"/>
+      <c r="U35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n"/>
@@ -2706,8 +2748,8 @@
       <c r="P36" s="13" t="n"/>
       <c r="Q36" s="13" t="n"/>
       <c r="R36" s="13" t="n"/>
-      <c r="S36" s="13" t="n"/>
-      <c r="T36" s="24" t="n"/>
+      <c r="T36" s="13" t="n"/>
+      <c r="U36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n"/>
@@ -2728,8 +2770,8 @@
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
-      <c r="S37" s="9" t="n"/>
-      <c r="T37" s="22" t="n"/>
+      <c r="T37" s="9" t="n"/>
+      <c r="U37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n"/>
@@ -2750,8 +2792,8 @@
       <c r="P38" s="13" t="n"/>
       <c r="Q38" s="13" t="n"/>
       <c r="R38" s="13" t="n"/>
-      <c r="S38" s="13" t="n"/>
-      <c r="T38" s="24" t="n"/>
+      <c r="T38" s="13" t="n"/>
+      <c r="U38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n"/>
@@ -2772,8 +2814,8 @@
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
-      <c r="S39" s="9" t="n"/>
-      <c r="T39" s="22" t="n"/>
+      <c r="T39" s="9" t="n"/>
+      <c r="U39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n"/>
@@ -2794,8 +2836,8 @@
       <c r="P40" s="13" t="n"/>
       <c r="Q40" s="13" t="n"/>
       <c r="R40" s="13" t="n"/>
-      <c r="S40" s="13" t="n"/>
-      <c r="T40" s="24" t="n"/>
+      <c r="T40" s="13" t="n"/>
+      <c r="U40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n"/>
@@ -2816,8 +2858,8 @@
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
-      <c r="S41" s="9" t="n"/>
-      <c r="T41" s="22" t="n"/>
+      <c r="T41" s="9" t="n"/>
+      <c r="U41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n"/>
@@ -2838,8 +2880,8 @@
       <c r="P42" s="13" t="n"/>
       <c r="Q42" s="13" t="n"/>
       <c r="R42" s="13" t="n"/>
-      <c r="S42" s="13" t="n"/>
-      <c r="T42" s="24" t="n"/>
+      <c r="T42" s="13" t="n"/>
+      <c r="U42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n"/>
@@ -2860,8 +2902,8 @@
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
-      <c r="S43" s="9" t="n"/>
-      <c r="T43" s="22" t="n"/>
+      <c r="T43" s="9" t="n"/>
+      <c r="U43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n"/>
@@ -2882,8 +2924,8 @@
       <c r="P44" s="13" t="n"/>
       <c r="Q44" s="13" t="n"/>
       <c r="R44" s="13" t="n"/>
-      <c r="S44" s="13" t="n"/>
-      <c r="T44" s="24" t="n"/>
+      <c r="T44" s="13" t="n"/>
+      <c r="U44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n"/>
@@ -2904,8 +2946,8 @@
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
-      <c r="S45" s="9" t="n"/>
-      <c r="T45" s="22" t="n"/>
+      <c r="T45" s="9" t="n"/>
+      <c r="U45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n"/>
@@ -2926,8 +2968,8 @@
       <c r="P46" s="13" t="n"/>
       <c r="Q46" s="13" t="n"/>
       <c r="R46" s="13" t="n"/>
-      <c r="S46" s="13" t="n"/>
-      <c r="T46" s="24" t="n"/>
+      <c r="T46" s="13" t="n"/>
+      <c r="U46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n"/>
@@ -2948,8 +2990,8 @@
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
-      <c r="S47" s="9" t="n"/>
-      <c r="T47" s="22" t="n"/>
+      <c r="T47" s="9" t="n"/>
+      <c r="U47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n"/>
@@ -2970,8 +3012,8 @@
       <c r="P48" s="13" t="n"/>
       <c r="Q48" s="13" t="n"/>
       <c r="R48" s="13" t="n"/>
-      <c r="S48" s="13" t="n"/>
-      <c r="T48" s="24" t="n"/>
+      <c r="T48" s="13" t="n"/>
+      <c r="U48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n"/>
@@ -2992,8 +3034,8 @@
       <c r="P49" s="9" t="n"/>
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
-      <c r="S49" s="9" t="n"/>
-      <c r="T49" s="22" t="n"/>
+      <c r="T49" s="9" t="n"/>
+      <c r="U49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n"/>
@@ -3014,8 +3056,8 @@
       <c r="P50" s="13" t="n"/>
       <c r="Q50" s="13" t="n"/>
       <c r="R50" s="13" t="n"/>
-      <c r="S50" s="13" t="n"/>
-      <c r="T50" s="24" t="n"/>
+      <c r="T50" s="13" t="n"/>
+      <c r="U50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n"/>
@@ -3036,8 +3078,8 @@
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
-      <c r="S51" s="9" t="n"/>
-      <c r="T51" s="22" t="n"/>
+      <c r="T51" s="9" t="n"/>
+      <c r="U51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n"/>
@@ -3058,8 +3100,8 @@
       <c r="P52" s="13" t="n"/>
       <c r="Q52" s="13" t="n"/>
       <c r="R52" s="13" t="n"/>
-      <c r="S52" s="13" t="n"/>
-      <c r="T52" s="24" t="n"/>
+      <c r="T52" s="13" t="n"/>
+      <c r="U52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n"/>
@@ -3080,8 +3122,8 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n"/>
-      <c r="T53" s="22" t="n"/>
+      <c r="T53" s="9" t="n"/>
+      <c r="U53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n"/>
@@ -3102,8 +3144,8 @@
       <c r="P54" s="13" t="n"/>
       <c r="Q54" s="13" t="n"/>
       <c r="R54" s="13" t="n"/>
-      <c r="S54" s="13" t="n"/>
-      <c r="T54" s="24" t="n"/>
+      <c r="T54" s="13" t="n"/>
+      <c r="U54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n"/>
@@ -3124,8 +3166,8 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="9" t="n"/>
-      <c r="T55" s="22" t="n"/>
+      <c r="T55" s="9" t="n"/>
+      <c r="U55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n"/>
@@ -3146,8 +3188,8 @@
       <c r="P56" s="13" t="n"/>
       <c r="Q56" s="13" t="n"/>
       <c r="R56" s="13" t="n"/>
-      <c r="S56" s="13" t="n"/>
-      <c r="T56" s="24" t="n"/>
+      <c r="T56" s="13" t="n"/>
+      <c r="U56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n"/>
@@ -3168,8 +3210,8 @@
       <c r="P57" s="9" t="n"/>
       <c r="Q57" s="9" t="n"/>
       <c r="R57" s="9" t="n"/>
-      <c r="S57" s="9" t="n"/>
-      <c r="T57" s="22" t="n"/>
+      <c r="T57" s="9" t="n"/>
+      <c r="U57" s="22" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -408,6 +408,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -652,6 +664,13 @@
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <t>▣ AUTORUN
+(직접 입력)</t>
+      </text>
+    </comment>
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
+        <t>▣ 가공
+입고일
 (직접 입력)</t>
       </text>
     </comment>
@@ -983,11 +1002,12 @@
     <col width="8" customWidth="1" style="55" min="17" max="17"/>
     <col width="9" customWidth="1" style="55" min="18" max="18"/>
     <col width="12" customWidth="1" style="55" min="19" max="19"/>
-    <col width="28" customWidth="1" style="55" min="20" max="20"/>
+    <col width="10" customWidth="1" style="55" min="20" max="20"/>
+    <col width="28" customWidth="1" style="55" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 베트남 │ 2026</t>
         </is>
@@ -1009,11 +1029,12 @@
       <c r="P1" s="16" t="n"/>
       <c r="Q1" s="16" t="n"/>
       <c r="R1" s="16" t="n"/>
+      <c r="S1" s="16" t="n"/>
       <c r="T1" s="16" t="n"/>
       <c r="U1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="68" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 베트남 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1035,10 +1056,11 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="16" t="n"/>
+      <c r="S2" s="16" t="n"/>
       <c r="T2" s="17" t="n"/>
-      <c r="U2" s="64" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:42</t>
+      <c r="U2" s="69" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:45</t>
         </is>
       </c>
     </row>
@@ -1133,9 +1155,9 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="S3" s="65" t="inlineStr">
-        <is>
-          <t>✏입력</t>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
@@ -1240,7 +1262,7 @@
           <t>AUTORUN</t>
         </is>
       </c>
-      <c r="S4" s="66" t="inlineStr">
+      <c r="S4" s="70" t="inlineStr">
         <is>
           <t>가공
 입고일</t>
@@ -1312,6 +1334,7 @@
       <c r="P5" s="11" t="n"/>
       <c r="Q5" s="11" t="n"/>
       <c r="R5" s="11" t="n"/>
+      <c r="S5" s="9" t="n"/>
       <c r="T5" s="9" t="n"/>
       <c r="U5" s="22" t="n"/>
     </row>
@@ -1370,6 +1393,7 @@
       <c r="P6" s="15" t="n"/>
       <c r="Q6" s="15" t="n"/>
       <c r="R6" s="15" t="n"/>
+      <c r="S6" s="13" t="n"/>
       <c r="T6" s="13" t="n"/>
       <c r="U6" s="24" t="n"/>
     </row>
@@ -1426,6 +1450,7 @@
       <c r="P7" s="11" t="n"/>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="11" t="n"/>
+      <c r="S7" s="9" t="n"/>
       <c r="T7" s="9" t="n"/>
       <c r="U7" s="22" t="n"/>
     </row>
@@ -1482,6 +1507,7 @@
       <c r="P8" s="15" t="n"/>
       <c r="Q8" s="15" t="n"/>
       <c r="R8" s="15" t="n"/>
+      <c r="S8" s="13" t="n"/>
       <c r="T8" s="13" t="n"/>
       <c r="U8" s="24" t="n"/>
     </row>
@@ -1538,6 +1564,7 @@
       <c r="P9" s="11" t="n"/>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="11" t="n"/>
+      <c r="S9" s="9" t="n"/>
       <c r="T9" s="9" t="n"/>
       <c r="U9" s="22" t="n"/>
     </row>
@@ -1594,6 +1621,7 @@
       <c r="P10" s="15" t="n"/>
       <c r="Q10" s="15" t="n"/>
       <c r="R10" s="15" t="n"/>
+      <c r="S10" s="13" t="n"/>
       <c r="T10" s="13" t="n"/>
       <c r="U10" s="24" t="n"/>
     </row>
@@ -1650,6 +1678,7 @@
       <c r="P11" s="11" t="n"/>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="11" t="n"/>
+      <c r="S11" s="9" t="n"/>
       <c r="T11" s="9" t="n"/>
       <c r="U11" s="22" t="n"/>
     </row>
@@ -1706,6 +1735,7 @@
       <c r="P12" s="15" t="n"/>
       <c r="Q12" s="15" t="n"/>
       <c r="R12" s="15" t="n"/>
+      <c r="S12" s="13" t="n"/>
       <c r="T12" s="13" t="n"/>
       <c r="U12" s="24" t="n"/>
     </row>
@@ -1762,6 +1792,7 @@
       <c r="P13" s="11" t="n"/>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="11" t="n"/>
+      <c r="S13" s="9" t="n"/>
       <c r="T13" s="9" t="n"/>
       <c r="U13" s="22" t="n"/>
     </row>
@@ -1818,6 +1849,7 @@
       <c r="P14" s="15" t="n"/>
       <c r="Q14" s="15" t="n"/>
       <c r="R14" s="15" t="n"/>
+      <c r="S14" s="13" t="n"/>
       <c r="T14" s="13" t="n"/>
       <c r="U14" s="24" t="n"/>
     </row>
@@ -1874,6 +1906,7 @@
       <c r="P15" s="11" t="n"/>
       <c r="Q15" s="11" t="n"/>
       <c r="R15" s="11" t="n"/>
+      <c r="S15" s="9" t="n"/>
       <c r="T15" s="9" t="n"/>
       <c r="U15" s="22" t="n"/>
     </row>
@@ -1932,6 +1965,7 @@
       <c r="P16" s="15" t="n"/>
       <c r="Q16" s="15" t="n"/>
       <c r="R16" s="15" t="n"/>
+      <c r="S16" s="13" t="n"/>
       <c r="T16" s="13" t="n"/>
       <c r="U16" s="24" t="n"/>
     </row>
@@ -1990,6 +2024,7 @@
       <c r="P17" s="11" t="n"/>
       <c r="Q17" s="11" t="n"/>
       <c r="R17" s="11" t="n"/>
+      <c r="S17" s="9" t="n"/>
       <c r="T17" s="9" t="n"/>
       <c r="U17" s="22" t="n"/>
     </row>
@@ -2046,6 +2081,7 @@
       <c r="P18" s="15" t="n"/>
       <c r="Q18" s="15" t="n"/>
       <c r="R18" s="15" t="n"/>
+      <c r="S18" s="13" t="n"/>
       <c r="T18" s="13" t="n"/>
       <c r="U18" s="24" t="n"/>
     </row>
@@ -2102,6 +2138,7 @@
       <c r="P19" s="11" t="n"/>
       <c r="Q19" s="11" t="n"/>
       <c r="R19" s="11" t="n"/>
+      <c r="S19" s="9" t="n"/>
       <c r="T19" s="9" t="n"/>
       <c r="U19" s="22" t="n"/>
     </row>
@@ -2158,6 +2195,7 @@
       <c r="P20" s="15" t="n"/>
       <c r="Q20" s="15" t="n"/>
       <c r="R20" s="15" t="n"/>
+      <c r="S20" s="13" t="n"/>
       <c r="T20" s="13" t="n"/>
       <c r="U20" s="24" t="n"/>
     </row>
@@ -2214,6 +2252,7 @@
       <c r="P21" s="11" t="n"/>
       <c r="Q21" s="11" t="n"/>
       <c r="R21" s="11" t="n"/>
+      <c r="S21" s="9" t="n"/>
       <c r="T21" s="9" t="n"/>
       <c r="U21" s="22" t="n"/>
     </row>
@@ -2270,6 +2309,7 @@
       <c r="P22" s="15" t="n"/>
       <c r="Q22" s="15" t="n"/>
       <c r="R22" s="15" t="n"/>
+      <c r="S22" s="13" t="n"/>
       <c r="T22" s="13" t="n"/>
       <c r="U22" s="24" t="n"/>
     </row>
@@ -2326,6 +2366,7 @@
       <c r="P23" s="11" t="n"/>
       <c r="Q23" s="11" t="n"/>
       <c r="R23" s="11" t="n"/>
+      <c r="S23" s="9" t="n"/>
       <c r="T23" s="9" t="n"/>
       <c r="U23" s="22" t="n"/>
     </row>
@@ -2382,6 +2423,7 @@
       <c r="P24" s="15" t="n"/>
       <c r="Q24" s="15" t="n"/>
       <c r="R24" s="15" t="n"/>
+      <c r="S24" s="13" t="n"/>
       <c r="T24" s="13" t="n"/>
       <c r="U24" s="24" t="n"/>
     </row>
@@ -2438,6 +2480,7 @@
       <c r="P25" s="11" t="n"/>
       <c r="Q25" s="11" t="n"/>
       <c r="R25" s="11" t="n"/>
+      <c r="S25" s="9" t="n"/>
       <c r="T25" s="9" t="n"/>
       <c r="U25" s="22" t="n"/>
     </row>
@@ -2494,6 +2537,7 @@
       <c r="P26" s="15" t="n"/>
       <c r="Q26" s="15" t="n"/>
       <c r="R26" s="15" t="n"/>
+      <c r="S26" s="13" t="n"/>
       <c r="T26" s="13" t="n"/>
       <c r="U26" s="24" t="n"/>
     </row>
@@ -2550,6 +2594,7 @@
       <c r="P27" s="11" t="n"/>
       <c r="Q27" s="11" t="n"/>
       <c r="R27" s="11" t="n"/>
+      <c r="S27" s="9" t="n"/>
       <c r="T27" s="9" t="n"/>
       <c r="U27" s="22" t="n"/>
     </row>
@@ -2572,6 +2617,7 @@
       <c r="P28" s="13" t="n"/>
       <c r="Q28" s="13" t="n"/>
       <c r="R28" s="13" t="n"/>
+      <c r="S28" s="13" t="n"/>
       <c r="T28" s="13" t="n"/>
       <c r="U28" s="24" t="n"/>
     </row>
@@ -2594,6 +2640,7 @@
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
+      <c r="S29" s="9" t="n"/>
       <c r="T29" s="9" t="n"/>
       <c r="U29" s="22" t="n"/>
     </row>
@@ -2616,6 +2663,7 @@
       <c r="P30" s="13" t="n"/>
       <c r="Q30" s="13" t="n"/>
       <c r="R30" s="13" t="n"/>
+      <c r="S30" s="13" t="n"/>
       <c r="T30" s="13" t="n"/>
       <c r="U30" s="24" t="n"/>
     </row>
@@ -2638,6 +2686,7 @@
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n"/>
       <c r="R31" s="9" t="n"/>
+      <c r="S31" s="9" t="n"/>
       <c r="T31" s="9" t="n"/>
       <c r="U31" s="22" t="n"/>
     </row>
@@ -2660,6 +2709,7 @@
       <c r="P32" s="13" t="n"/>
       <c r="Q32" s="13" t="n"/>
       <c r="R32" s="13" t="n"/>
+      <c r="S32" s="13" t="n"/>
       <c r="T32" s="13" t="n"/>
       <c r="U32" s="24" t="n"/>
     </row>
@@ -2682,6 +2732,7 @@
       <c r="P33" s="9" t="n"/>
       <c r="Q33" s="9" t="n"/>
       <c r="R33" s="9" t="n"/>
+      <c r="S33" s="9" t="n"/>
       <c r="T33" s="9" t="n"/>
       <c r="U33" s="22" t="n"/>
     </row>
@@ -2704,6 +2755,7 @@
       <c r="P34" s="13" t="n"/>
       <c r="Q34" s="13" t="n"/>
       <c r="R34" s="13" t="n"/>
+      <c r="S34" s="13" t="n"/>
       <c r="T34" s="13" t="n"/>
       <c r="U34" s="24" t="n"/>
     </row>
@@ -2726,6 +2778,7 @@
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
       <c r="R35" s="9" t="n"/>
+      <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="22" t="n"/>
     </row>
@@ -2748,6 +2801,7 @@
       <c r="P36" s="13" t="n"/>
       <c r="Q36" s="13" t="n"/>
       <c r="R36" s="13" t="n"/>
+      <c r="S36" s="13" t="n"/>
       <c r="T36" s="13" t="n"/>
       <c r="U36" s="24" t="n"/>
     </row>
@@ -2770,6 +2824,7 @@
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
+      <c r="S37" s="9" t="n"/>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="22" t="n"/>
     </row>
@@ -2792,6 +2847,7 @@
       <c r="P38" s="13" t="n"/>
       <c r="Q38" s="13" t="n"/>
       <c r="R38" s="13" t="n"/>
+      <c r="S38" s="13" t="n"/>
       <c r="T38" s="13" t="n"/>
       <c r="U38" s="24" t="n"/>
     </row>
@@ -2814,6 +2870,7 @@
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
+      <c r="S39" s="9" t="n"/>
       <c r="T39" s="9" t="n"/>
       <c r="U39" s="22" t="n"/>
     </row>
@@ -2836,6 +2893,7 @@
       <c r="P40" s="13" t="n"/>
       <c r="Q40" s="13" t="n"/>
       <c r="R40" s="13" t="n"/>
+      <c r="S40" s="13" t="n"/>
       <c r="T40" s="13" t="n"/>
       <c r="U40" s="24" t="n"/>
     </row>
@@ -2858,6 +2916,7 @@
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
+      <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="22" t="n"/>
     </row>
@@ -2880,6 +2939,7 @@
       <c r="P42" s="13" t="n"/>
       <c r="Q42" s="13" t="n"/>
       <c r="R42" s="13" t="n"/>
+      <c r="S42" s="13" t="n"/>
       <c r="T42" s="13" t="n"/>
       <c r="U42" s="24" t="n"/>
     </row>
@@ -2902,6 +2962,7 @@
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
+      <c r="S43" s="9" t="n"/>
       <c r="T43" s="9" t="n"/>
       <c r="U43" s="22" t="n"/>
     </row>
@@ -2924,6 +2985,7 @@
       <c r="P44" s="13" t="n"/>
       <c r="Q44" s="13" t="n"/>
       <c r="R44" s="13" t="n"/>
+      <c r="S44" s="13" t="n"/>
       <c r="T44" s="13" t="n"/>
       <c r="U44" s="24" t="n"/>
     </row>
@@ -2946,6 +3008,7 @@
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
+      <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="22" t="n"/>
     </row>
@@ -2968,6 +3031,7 @@
       <c r="P46" s="13" t="n"/>
       <c r="Q46" s="13" t="n"/>
       <c r="R46" s="13" t="n"/>
+      <c r="S46" s="13" t="n"/>
       <c r="T46" s="13" t="n"/>
       <c r="U46" s="24" t="n"/>
     </row>
@@ -2990,6 +3054,7 @@
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
+      <c r="S47" s="9" t="n"/>
       <c r="T47" s="9" t="n"/>
       <c r="U47" s="22" t="n"/>
     </row>
@@ -3012,6 +3077,7 @@
       <c r="P48" s="13" t="n"/>
       <c r="Q48" s="13" t="n"/>
       <c r="R48" s="13" t="n"/>
+      <c r="S48" s="13" t="n"/>
       <c r="T48" s="13" t="n"/>
       <c r="U48" s="24" t="n"/>
     </row>
@@ -3034,6 +3100,7 @@
       <c r="P49" s="9" t="n"/>
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
+      <c r="S49" s="9" t="n"/>
       <c r="T49" s="9" t="n"/>
       <c r="U49" s="22" t="n"/>
     </row>
@@ -3056,6 +3123,7 @@
       <c r="P50" s="13" t="n"/>
       <c r="Q50" s="13" t="n"/>
       <c r="R50" s="13" t="n"/>
+      <c r="S50" s="13" t="n"/>
       <c r="T50" s="13" t="n"/>
       <c r="U50" s="24" t="n"/>
     </row>
@@ -3078,6 +3146,7 @@
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
+      <c r="S51" s="9" t="n"/>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="22" t="n"/>
     </row>
@@ -3100,6 +3169,7 @@
       <c r="P52" s="13" t="n"/>
       <c r="Q52" s="13" t="n"/>
       <c r="R52" s="13" t="n"/>
+      <c r="S52" s="13" t="n"/>
       <c r="T52" s="13" t="n"/>
       <c r="U52" s="24" t="n"/>
     </row>
@@ -3122,6 +3192,7 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
+      <c r="S53" s="9" t="n"/>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="22" t="n"/>
     </row>
@@ -3144,6 +3215,7 @@
       <c r="P54" s="13" t="n"/>
       <c r="Q54" s="13" t="n"/>
       <c r="R54" s="13" t="n"/>
+      <c r="S54" s="13" t="n"/>
       <c r="T54" s="13" t="n"/>
       <c r="U54" s="24" t="n"/>
     </row>
@@ -3166,6 +3238,7 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
+      <c r="S55" s="9" t="n"/>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="22" t="n"/>
     </row>
@@ -3188,6 +3261,7 @@
       <c r="P56" s="13" t="n"/>
       <c r="Q56" s="13" t="n"/>
       <c r="R56" s="13" t="n"/>
+      <c r="S56" s="13" t="n"/>
       <c r="T56" s="13" t="n"/>
       <c r="U56" s="24" t="n"/>
     </row>
@@ -3210,14 +3284,15 @@
       <c r="P57" s="9" t="n"/>
       <c r="Q57" s="9" t="n"/>
       <c r="R57" s="9" t="n"/>
+      <c r="S57" s="9" t="n"/>
       <c r="T57" s="9" t="n"/>
       <c r="U57" s="22" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:T2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="S5:S28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -421,6 +421,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -612,8 +630,11 @@
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당자
-(직접 입력)</t>
+        <t>▣ 부서 담당자
+• 부서 내 실제 담당자 이름 입력
+  예: 정민규, 한재운, 이찬
+• 입력 시: PMS에도 자동 반영
+• 빈 칸: 부서 참여 확정, 담당자 미정</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
@@ -627,63 +648,110 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계
-(직접 입력)</t>
+        <t>▣ 설계 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ SW
-(직접 입력)</t>
+        <t>▣ SW (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전장
-(직접 입력)</t>
+        <t>▣ 전장 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공
-(직접 입력)</t>
+        <t>▣ 가공 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 조립
-(직접 입력)</t>
+        <t>▣ 조립 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ DRYRUN
-(직접 입력)</t>
+        <t>▣ DRYRUN (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ AUTORUN
-(직접 입력)</t>
+        <t>▣ AUTORUN (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공
-입고일
-(직접 입력)</t>
+        <t>▣ 가공 입고일 (베트남)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD
+• 베트남 외주 가공품 실제 입고일
+• 비워두면 진행중 / 입력 시 입고완료</t>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상태
-(직접 입력)</t>
+        <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모
-(직접 입력)</t>
+        <t>▣ 메모 (부서 자유 입력)
+• 자유 텍스트 입력
+• 활용:
+  - 이슈사항 (예: 자재 결품, 외주 지연)
+  - 변경 요청 (예: 사양 변경, 납기 조정)
+  - 다른 부서·PM에게 공유할 정보
+• 대시보드 집계에는 미포함</t>
       </text>
     </comment>
   </commentList>
@@ -1007,7 +1075,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 베트남 │ 2026</t>
         </is>
@@ -1034,7 +1102,7 @@
       <c r="U1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="68" t="inlineStr">
+      <c r="A2" s="75" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 베트남 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1058,9 +1126,9 @@
       <c r="R2" s="16" t="n"/>
       <c r="S2" s="16" t="n"/>
       <c r="T2" s="17" t="n"/>
-      <c r="U2" s="69" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:45</t>
+      <c r="U2" s="76" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -421,6 +421,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1075,7 +1084,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="74" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 베트남 │ 2026</t>
         </is>
@@ -1102,7 +1111,7 @@
       <c r="U1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="75" t="inlineStr">
+      <c r="A2" s="78" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 베트남 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1126,9 +1135,9 @@
       <c r="R2" s="16" t="n"/>
       <c r="S2" s="16" t="n"/>
       <c r="T2" s="17" t="n"/>
-      <c r="U2" s="76" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="U2" s="79" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:01</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -421,6 +421,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -648,11 +657,15 @@
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+• 자동 계산 (수정 불가, sync 시 갱신)
+• 시작일·완료일 입력 기반:
+    0%  = 미착수    (시작일·완료일 모두 빈 칸)
+   50%  = 진행중    (시작일만 입력)
+  100%  = 완료      (완료일까지 입력)
+• ★ 이 값은 '이 부서'만의 진척률입니다.
+• 프로젝트 전체 진척률은 PMS 1_프로젝트등록
+  '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
@@ -1084,7 +1097,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="77" t="inlineStr">
+      <c r="A1" s="80" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 베트남 │ 2026</t>
         </is>
@@ -1111,7 +1124,7 @@
       <c r="U1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 베트남 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1135,9 +1148,9 @@
       <c r="R2" s="16" t="n"/>
       <c r="S2" s="16" t="n"/>
       <c r="T2" s="17" t="n"/>
-      <c r="U2" s="79" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:01</t>
+      <c r="U2" s="82" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:54</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1314,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>전체진척률(%)</t>
+          <t>부서진척률(%)</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -1402,7 +1415,7 @@
       </c>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="10" t="n">
-        <v>0.009166666666666667</v>
+        <v>0</v>
       </c>
       <c r="L5" s="11" t="n"/>
       <c r="M5" s="11" t="n"/>
@@ -1461,7 +1474,7 @@
       </c>
       <c r="J6" s="13" t="n"/>
       <c r="K6" s="14" t="n">
-        <v>0.007800000000000001</v>
+        <v>0</v>
       </c>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
@@ -1519,7 +1532,9 @@
         </is>
       </c>
       <c r="J7" s="9" t="n"/>
-      <c r="K7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="11" t="n"/>
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
@@ -1576,7 +1591,9 @@
         </is>
       </c>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="14" t="inlineStr"/>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="15" t="n"/>
       <c r="M8" s="15" t="n"/>
       <c r="N8" s="15" t="n"/>
@@ -1633,7 +1650,9 @@
         </is>
       </c>
       <c r="J9" s="9" t="n"/>
-      <c r="K9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" s="11" t="n"/>
       <c r="M9" s="11" t="n"/>
       <c r="N9" s="11" t="n"/>
@@ -1690,7 +1709,9 @@
         </is>
       </c>
       <c r="J10" s="13" t="n"/>
-      <c r="K10" s="14" t="inlineStr"/>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
       <c r="N10" s="15" t="n"/>
@@ -1747,7 +1768,9 @@
         </is>
       </c>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="10" t="inlineStr"/>
+      <c r="K11" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="11" t="n"/>
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
@@ -1804,7 +1827,9 @@
         </is>
       </c>
       <c r="J12" s="13" t="n"/>
-      <c r="K12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
       <c r="N12" s="15" t="n"/>
@@ -1861,7 +1886,9 @@
         </is>
       </c>
       <c r="J13" s="9" t="n"/>
-      <c r="K13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="11" t="n"/>
       <c r="M13" s="11" t="n"/>
       <c r="N13" s="11" t="n"/>
@@ -1918,7 +1945,9 @@
         </is>
       </c>
       <c r="J14" s="13" t="n"/>
-      <c r="K14" s="14" t="inlineStr"/>
+      <c r="K14" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
       <c r="N14" s="15" t="n"/>
@@ -1975,7 +2004,9 @@
         </is>
       </c>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="11" t="n"/>
@@ -2033,7 +2064,7 @@
       </c>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="14" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
@@ -2092,7 +2123,7 @@
       </c>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="11" t="n"/>
@@ -2150,7 +2181,9 @@
         </is>
       </c>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -2207,7 +2240,9 @@
         </is>
       </c>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="10" t="inlineStr"/>
+      <c r="K19" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" s="11" t="n"/>
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="11" t="n"/>
@@ -2264,7 +2299,9 @@
         </is>
       </c>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
@@ -2321,7 +2358,9 @@
         </is>
       </c>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" s="11" t="n"/>
       <c r="M21" s="11" t="n"/>
       <c r="N21" s="11" t="n"/>
@@ -2378,7 +2417,9 @@
         </is>
       </c>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="14" t="inlineStr"/>
+      <c r="K22" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
@@ -2435,7 +2476,9 @@
         </is>
       </c>
       <c r="J23" s="9" t="n"/>
-      <c r="K23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L23" s="11" t="n"/>
       <c r="M23" s="11" t="n"/>
       <c r="N23" s="11" t="n"/>
@@ -2492,7 +2535,9 @@
         </is>
       </c>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="14" t="inlineStr"/>
+      <c r="K24" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
       <c r="N24" s="15" t="n"/>
@@ -2549,7 +2594,9 @@
         </is>
       </c>
       <c r="J25" s="9" t="n"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L25" s="11" t="n"/>
       <c r="M25" s="11" t="n"/>
       <c r="N25" s="11" t="n"/>
@@ -2606,7 +2653,9 @@
         </is>
       </c>
       <c r="J26" s="13" t="n"/>
-      <c r="K26" s="14" t="inlineStr"/>
+      <c r="K26" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
       <c r="N26" s="15" t="n"/>
@@ -2663,7 +2712,9 @@
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -421,6 +421,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -542,15 +560,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -564,46 +597,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -614,11 +687,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -633,31 +714,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -666,114 +771,195 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 설계 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ SW (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ SW (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전장 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전장 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 조립 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 조립 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ DRYRUN (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ DRYRUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ AUTORUN (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ AUTORUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공 입고일 (베트남)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공 입고일 (베트남)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 베트남 외주 가공품 실제 입고일
 • 비워두면 진행중 / 입력 시 입고완료</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1097,7 +1283,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="80" t="inlineStr">
+      <c r="A1" s="86" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 베트남 │ 2026</t>
         </is>
@@ -1124,7 +1310,7 @@
       <c r="U1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="81" t="inlineStr">
+      <c r="A2" s="87" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 베트남 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1148,9 +1334,9 @@
       <c r="R2" s="16" t="n"/>
       <c r="S2" s="16" t="n"/>
       <c r="T2" s="17" t="n"/>
-      <c r="U2" s="82" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:54</t>
+      <c r="U2" s="88" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:34</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -124,7 +124,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -204,11 +204,40 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -476,6 +505,17 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1283,7 +1323,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="86" t="inlineStr">
+      <c r="A1" s="89" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 베트남 │ 2026</t>
         </is>
@@ -1310,7 +1350,7 @@
       <c r="U1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="87" t="inlineStr">
+      <c r="A2" s="90" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 베트남 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1331,14 +1371,14 @@
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
-      <c r="R2" s="16" t="n"/>
-      <c r="S2" s="16" t="n"/>
-      <c r="T2" s="17" t="n"/>
-      <c r="U2" s="88" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:34</t>
-        </is>
-      </c>
+      <c r="R2" s="17" t="n"/>
+      <c r="S2" s="91" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:56</t>
+        </is>
+      </c>
+      <c r="T2" s="92" t="n"/>
+      <c r="U2" s="93" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -3604,9 +3644,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="S2:U2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="S5:S28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -600,30 +609,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -637,86 +631,46 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -727,19 +681,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -754,55 +700,31 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 담당자
+        <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -811,195 +733,149 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 설계 (세부항목 진척률)
+        <t>▣ 설계 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ SW (세부항목 진척률)
+        <t>▣ SW (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전장 (세부항목 진척률)
+        <t>▣ 전장 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 가공 (세부항목 진척률)
+        <t>▣ 가공 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 조립 (세부항목 진척률)
+        <t>▣ 조립 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ DRYRUN (세부항목 진척률)
+        <t>▣ DRYRUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ AUTORUN (세부항목 진척률)
+        <t>▣ AUTORUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 가공 입고일 (베트남)
+        <t>▣ 가공 입고일 (베트남)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 베트남 외주 가공품 실제 입고일
 • 비워두면 진행중 / 입력 시 입고완료</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메모 (부서 자유 입력)
+        <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1310,20 +1186,20 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="55" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" style="55" min="12" max="12"/>
+    <col width="5" customWidth="1" style="55" min="12" max="12"/>
     <col width="5" customWidth="1" style="55" min="13" max="13"/>
-    <col width="6" customWidth="1" style="55" min="14" max="14"/>
-    <col width="6" customWidth="1" style="55" min="15" max="15"/>
-    <col width="6" customWidth="1" style="55" min="16" max="16"/>
-    <col width="8" customWidth="1" style="55" min="17" max="17"/>
-    <col width="9" customWidth="1" style="55" min="18" max="18"/>
-    <col width="12" customWidth="1" style="55" min="19" max="19"/>
+    <col width="5" customWidth="1" style="55" min="14" max="14"/>
+    <col width="5" customWidth="1" style="55" min="15" max="15"/>
+    <col width="5" customWidth="1" style="55" min="16" max="16"/>
+    <col width="5" customWidth="1" style="55" min="17" max="17"/>
+    <col width="5" customWidth="1" style="55" min="18" max="18"/>
+    <col width="5" customWidth="1" style="55" min="19" max="19"/>
     <col width="10" customWidth="1" style="55" min="20" max="20"/>
     <col width="28" customWidth="1" style="55" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="89" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 베트남 │ 2026</t>
         </is>
@@ -1350,7 +1226,7 @@
       <c r="U1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="90" t="inlineStr">
+      <c r="A2" s="95" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 베트남 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1372,13 +1248,13 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="17" t="n"/>
-      <c r="S2" s="91" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:56</t>
-        </is>
-      </c>
-      <c r="T2" s="92" t="n"/>
-      <c r="U2" s="93" t="n"/>
+      <c r="S2" s="96" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:27</t>
+        </is>
+      </c>
+      <c r="T2" s="16" t="n"/>
+      <c r="U2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1570,12 +1446,14 @@
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>DRYRUN</t>
+          <t>DRY
+RUN</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>AUTORUN</t>
+          <t>AUT
+ORUN</t>
         </is>
       </c>
       <c r="S4" s="70" t="inlineStr">
@@ -1640,8 +1518,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n"/>
-      <c r="K5" s="10" t="n">
-        <v>0</v>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L5" s="11" t="n"/>
       <c r="M5" s="11" t="n"/>
@@ -1699,8 +1579,10 @@
         </is>
       </c>
       <c r="J6" s="13" t="n"/>
-      <c r="K6" s="14" t="n">
-        <v>0</v>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
@@ -1758,8 +1640,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n"/>
-      <c r="K7" s="10" t="n">
-        <v>0</v>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L7" s="11" t="n"/>
       <c r="M7" s="11" t="n"/>
@@ -1817,8 +1701,10 @@
         </is>
       </c>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="14" t="n">
-        <v>0</v>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L8" s="15" t="n"/>
       <c r="M8" s="15" t="n"/>
@@ -1876,8 +1762,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n"/>
-      <c r="K9" s="10" t="n">
-        <v>0</v>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L9" s="11" t="n"/>
       <c r="M9" s="11" t="n"/>
@@ -1935,8 +1823,10 @@
         </is>
       </c>
       <c r="J10" s="13" t="n"/>
-      <c r="K10" s="14" t="n">
-        <v>0</v>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
@@ -1994,8 +1884,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="10" t="n">
-        <v>0</v>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L11" s="11" t="n"/>
       <c r="M11" s="11" t="n"/>
@@ -2053,8 +1945,10 @@
         </is>
       </c>
       <c r="J12" s="13" t="n"/>
-      <c r="K12" s="14" t="n">
-        <v>0</v>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -2112,8 +2006,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n"/>
-      <c r="K13" s="10" t="n">
-        <v>0</v>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L13" s="11" t="n"/>
       <c r="M13" s="11" t="n"/>
@@ -2171,8 +2067,10 @@
         </is>
       </c>
       <c r="J14" s="13" t="n"/>
-      <c r="K14" s="14" t="n">
-        <v>0</v>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -2230,8 +2128,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="10" t="n">
-        <v>0</v>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="11" t="n"/>
@@ -2289,8 +2189,10 @@
         </is>
       </c>
       <c r="J16" s="13" t="n"/>
-      <c r="K16" s="14" t="n">
-        <v>0</v>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
@@ -2348,8 +2250,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n"/>
-      <c r="K17" s="10" t="n">
-        <v>0</v>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="11" t="n"/>
@@ -2407,8 +2311,10 @@
         </is>
       </c>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="14" t="n">
-        <v>0</v>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
@@ -2466,8 +2372,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="10" t="n">
-        <v>0</v>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L19" s="11" t="n"/>
       <c r="M19" s="11" t="n"/>
@@ -2525,8 +2433,10 @@
         </is>
       </c>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="14" t="n">
-        <v>0</v>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
@@ -2584,8 +2494,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" s="10" t="n">
-        <v>0</v>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L21" s="11" t="n"/>
       <c r="M21" s="11" t="n"/>
@@ -2643,8 +2555,10 @@
         </is>
       </c>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="14" t="n">
-        <v>0</v>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
@@ -2702,8 +2616,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n"/>
-      <c r="K23" s="10" t="n">
-        <v>0</v>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L23" s="11" t="n"/>
       <c r="M23" s="11" t="n"/>
@@ -2761,8 +2677,10 @@
         </is>
       </c>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="14" t="n">
-        <v>0</v>
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
@@ -2820,8 +2738,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n"/>
-      <c r="K25" s="10" t="n">
-        <v>0</v>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L25" s="11" t="n"/>
       <c r="M25" s="11" t="n"/>
@@ -2879,8 +2799,10 @@
         </is>
       </c>
       <c r="J26" s="13" t="n"/>
-      <c r="K26" s="14" t="n">
-        <v>0</v>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
@@ -2938,8 +2860,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="10" t="n">
-        <v>0</v>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="11" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -609,15 +618,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -631,46 +655,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -681,11 +745,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -700,31 +772,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -733,11 +829,19 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 설계 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -749,11 +853,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ SW (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ SW (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -765,11 +877,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전장 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전장 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -781,11 +901,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -797,11 +925,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 조립 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 조립 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -813,11 +949,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ DRYRUN (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ DRYRUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -829,11 +973,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ AUTORUN (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ AUTORUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -845,37 +997,62 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공 입고일 (베트남)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공 입고일 (베트남)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 베트남 외주 가공품 실제 입고일
 • 비워두면 진행중 / 입력 시 입고완료</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1186,20 +1363,20 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="55" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" style="55" min="12" max="12"/>
-    <col width="5" customWidth="1" style="55" min="13" max="13"/>
-    <col width="5" customWidth="1" style="55" min="14" max="14"/>
-    <col width="5" customWidth="1" style="55" min="15" max="15"/>
-    <col width="5" customWidth="1" style="55" min="16" max="16"/>
-    <col width="5" customWidth="1" style="55" min="17" max="17"/>
-    <col width="5" customWidth="1" style="55" min="18" max="18"/>
-    <col width="5" customWidth="1" style="55" min="19" max="19"/>
+    <col width="7" customWidth="1" style="55" min="12" max="12"/>
+    <col width="7" customWidth="1" style="55" min="13" max="13"/>
+    <col width="7" customWidth="1" style="55" min="14" max="14"/>
+    <col width="7" customWidth="1" style="55" min="15" max="15"/>
+    <col width="7" customWidth="1" style="55" min="16" max="16"/>
+    <col width="7" customWidth="1" style="55" min="17" max="17"/>
+    <col width="7" customWidth="1" style="55" min="18" max="18"/>
+    <col width="7" customWidth="1" style="55" min="19" max="19"/>
     <col width="10" customWidth="1" style="55" min="20" max="20"/>
     <col width="28" customWidth="1" style="55" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="94" t="inlineStr">
+      <c r="A1" s="97" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 베트남 │ 2026</t>
         </is>
@@ -1226,7 +1403,7 @@
       <c r="U1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="95" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 베트남 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1248,9 +1425,9 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="17" t="n"/>
-      <c r="S2" s="96" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:27</t>
+      <c r="S2" s="99" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="T2" s="16" t="n"/>
@@ -1452,8 +1629,8 @@
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>AUT
-ORUN</t>
+          <t>AUTO
+RUN</t>
         </is>
       </c>
       <c r="S4" s="70" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -618,30 +627,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -655,86 +649,46 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -745,19 +699,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -772,55 +718,31 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 담당자
+        <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -829,19 +751,11 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 설계 (세부항목 진척률)
+        <t>▣ 설계 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -853,19 +767,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ SW (세부항목 진척률)
+        <t>▣ SW (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -877,19 +783,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전장 (세부항목 진척률)
+        <t>▣ 전장 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -901,19 +799,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 가공 (세부항목 진척률)
+        <t>▣ 가공 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -925,19 +815,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 조립 (세부항목 진척률)
+        <t>▣ 조립 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -949,19 +831,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ DRYRUN (세부항목 진척률)
+        <t>▣ DRYRUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -973,19 +847,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ AUTORUN (세부항목 진척률)
+        <t>▣ AUTORUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -997,62 +863,49 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 가공 입고일 (베트남)
+        <t>▣ 가공 입고예정일 (베트남)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 베트남 가공 발주 시 ★입고 완료 예정일★ 기입
+• 베트남 자체 가공 또는 외주 가공 모두 해당
+📋 운영:
+  ▸ 발주 시 예정일 입력
+  ▸ 실제 입고일과 비교 → 지연 여부 추적</t>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0" shapeId="0">
+      <text>
+        <t>▣ 가공 입고일 (베트남)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 베트남 외주 가공품 실제 입고일
 • 비워두면 진행중 / 입력 시 입고완료</t>
-        </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메모 (부서 자유 입력)
+        <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1349,7 +1202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1371,12 +1224,13 @@
     <col width="7" customWidth="1" style="55" min="17" max="17"/>
     <col width="7" customWidth="1" style="55" min="18" max="18"/>
     <col width="7" customWidth="1" style="55" min="19" max="19"/>
-    <col width="10" customWidth="1" style="55" min="20" max="20"/>
-    <col width="28" customWidth="1" style="55" min="21" max="21"/>
+    <col width="7" customWidth="1" style="55" min="20" max="20"/>
+    <col width="10" customWidth="1" style="55" min="21" max="21"/>
+    <col width="28" customWidth="1" style="55" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="97" t="inlineStr">
+      <c r="A1" s="100" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 베트남 │ 2026</t>
         </is>
@@ -1400,10 +1254,11 @@
       <c r="R1" s="16" t="n"/>
       <c r="S1" s="16" t="n"/>
       <c r="T1" s="16" t="n"/>
-      <c r="U1" s="17" t="n"/>
+      <c r="U1" s="16" t="n"/>
+      <c r="V1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 베트남 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1424,14 +1279,15 @@
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
-      <c r="R2" s="17" t="n"/>
-      <c r="S2" s="99" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
-        </is>
-      </c>
-      <c r="T2" s="16" t="n"/>
-      <c r="U2" s="17" t="n"/>
+      <c r="R2" s="16" t="n"/>
+      <c r="S2" s="17" t="n"/>
+      <c r="T2" s="102" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:47</t>
+        </is>
+      </c>
+      <c r="U2" s="16" t="n"/>
+      <c r="V2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1529,12 +1385,17 @@
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1636,15 +1497,21 @@
       <c r="S4" s="70" t="inlineStr">
         <is>
           <t>가공
+예정일</t>
+        </is>
+      </c>
+      <c r="T4" s="70" t="inlineStr">
+        <is>
+          <t>가공
 입고일</t>
         </is>
       </c>
-      <c r="T4" s="7" t="inlineStr">
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="U4" s="7" t="inlineStr">
+      <c r="V4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1709,7 +1576,8 @@
       <c r="R5" s="11" t="n"/>
       <c r="S5" s="9" t="n"/>
       <c r="T5" s="9" t="n"/>
-      <c r="U5" s="22" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1770,7 +1638,8 @@
       <c r="R6" s="15" t="n"/>
       <c r="S6" s="13" t="n"/>
       <c r="T6" s="13" t="n"/>
-      <c r="U6" s="24" t="n"/>
+      <c r="U6" s="13" t="n"/>
+      <c r="V6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1831,7 +1700,8 @@
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="9" t="n"/>
       <c r="T7" s="9" t="n"/>
-      <c r="U7" s="22" t="n"/>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1892,7 +1762,8 @@
       <c r="R8" s="15" t="n"/>
       <c r="S8" s="13" t="n"/>
       <c r="T8" s="13" t="n"/>
-      <c r="U8" s="24" t="n"/>
+      <c r="U8" s="13" t="n"/>
+      <c r="V8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1953,7 +1824,8 @@
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="9" t="n"/>
       <c r="T9" s="9" t="n"/>
-      <c r="U9" s="22" t="n"/>
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -2014,7 +1886,8 @@
       <c r="R10" s="15" t="n"/>
       <c r="S10" s="13" t="n"/>
       <c r="T10" s="13" t="n"/>
-      <c r="U10" s="24" t="n"/>
+      <c r="U10" s="13" t="n"/>
+      <c r="V10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -2075,7 +1948,8 @@
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="9" t="n"/>
       <c r="T11" s="9" t="n"/>
-      <c r="U11" s="22" t="n"/>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -2136,7 +2010,8 @@
       <c r="R12" s="15" t="n"/>
       <c r="S12" s="13" t="n"/>
       <c r="T12" s="13" t="n"/>
-      <c r="U12" s="24" t="n"/>
+      <c r="U12" s="13" t="n"/>
+      <c r="V12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -2197,7 +2072,8 @@
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="9" t="n"/>
       <c r="T13" s="9" t="n"/>
-      <c r="U13" s="22" t="n"/>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -2258,7 +2134,8 @@
       <c r="R14" s="15" t="n"/>
       <c r="S14" s="13" t="n"/>
       <c r="T14" s="13" t="n"/>
-      <c r="U14" s="24" t="n"/>
+      <c r="U14" s="13" t="n"/>
+      <c r="V14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -2319,7 +2196,8 @@
       <c r="R15" s="11" t="n"/>
       <c r="S15" s="9" t="n"/>
       <c r="T15" s="9" t="n"/>
-      <c r="U15" s="22" t="n"/>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -2380,7 +2258,8 @@
       <c r="R16" s="15" t="n"/>
       <c r="S16" s="13" t="n"/>
       <c r="T16" s="13" t="n"/>
-      <c r="U16" s="24" t="n"/>
+      <c r="U16" s="13" t="n"/>
+      <c r="V16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -2441,7 +2320,8 @@
       <c r="R17" s="11" t="n"/>
       <c r="S17" s="9" t="n"/>
       <c r="T17" s="9" t="n"/>
-      <c r="U17" s="22" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -2502,7 +2382,8 @@
       <c r="R18" s="15" t="n"/>
       <c r="S18" s="13" t="n"/>
       <c r="T18" s="13" t="n"/>
-      <c r="U18" s="24" t="n"/>
+      <c r="U18" s="13" t="n"/>
+      <c r="V18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2563,7 +2444,8 @@
       <c r="R19" s="11" t="n"/>
       <c r="S19" s="9" t="n"/>
       <c r="T19" s="9" t="n"/>
-      <c r="U19" s="22" t="n"/>
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2624,7 +2506,8 @@
       <c r="R20" s="15" t="n"/>
       <c r="S20" s="13" t="n"/>
       <c r="T20" s="13" t="n"/>
-      <c r="U20" s="24" t="n"/>
+      <c r="U20" s="13" t="n"/>
+      <c r="V20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2685,7 +2568,8 @@
       <c r="R21" s="11" t="n"/>
       <c r="S21" s="9" t="n"/>
       <c r="T21" s="9" t="n"/>
-      <c r="U21" s="22" t="n"/>
+      <c r="U21" s="9" t="n"/>
+      <c r="V21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2746,7 +2630,8 @@
       <c r="R22" s="15" t="n"/>
       <c r="S22" s="13" t="n"/>
       <c r="T22" s="13" t="n"/>
-      <c r="U22" s="24" t="n"/>
+      <c r="U22" s="13" t="n"/>
+      <c r="V22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2807,7 +2692,8 @@
       <c r="R23" s="11" t="n"/>
       <c r="S23" s="9" t="n"/>
       <c r="T23" s="9" t="n"/>
-      <c r="U23" s="22" t="n"/>
+      <c r="U23" s="9" t="n"/>
+      <c r="V23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2868,7 +2754,8 @@
       <c r="R24" s="15" t="n"/>
       <c r="S24" s="13" t="n"/>
       <c r="T24" s="13" t="n"/>
-      <c r="U24" s="24" t="n"/>
+      <c r="U24" s="13" t="n"/>
+      <c r="V24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2929,7 +2816,8 @@
       <c r="R25" s="11" t="n"/>
       <c r="S25" s="9" t="n"/>
       <c r="T25" s="9" t="n"/>
-      <c r="U25" s="22" t="n"/>
+      <c r="U25" s="9" t="n"/>
+      <c r="V25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2990,7 +2878,8 @@
       <c r="R26" s="15" t="n"/>
       <c r="S26" s="13" t="n"/>
       <c r="T26" s="13" t="n"/>
-      <c r="U26" s="24" t="n"/>
+      <c r="U26" s="13" t="n"/>
+      <c r="V26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -3051,7 +2940,8 @@
       <c r="R27" s="11" t="n"/>
       <c r="S27" s="9" t="n"/>
       <c r="T27" s="9" t="n"/>
-      <c r="U27" s="22" t="n"/>
+      <c r="U27" s="9" t="n"/>
+      <c r="V27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n"/>
@@ -3074,7 +2964,8 @@
       <c r="R28" s="13" t="n"/>
       <c r="S28" s="13" t="n"/>
       <c r="T28" s="13" t="n"/>
-      <c r="U28" s="24" t="n"/>
+      <c r="U28" s="13" t="n"/>
+      <c r="V28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n"/>
@@ -3097,7 +2988,8 @@
       <c r="R29" s="9" t="n"/>
       <c r="S29" s="9" t="n"/>
       <c r="T29" s="9" t="n"/>
-      <c r="U29" s="22" t="n"/>
+      <c r="U29" s="9" t="n"/>
+      <c r="V29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n"/>
@@ -3120,7 +3012,8 @@
       <c r="R30" s="13" t="n"/>
       <c r="S30" s="13" t="n"/>
       <c r="T30" s="13" t="n"/>
-      <c r="U30" s="24" t="n"/>
+      <c r="U30" s="13" t="n"/>
+      <c r="V30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n"/>
@@ -3143,7 +3036,8 @@
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="9" t="n"/>
       <c r="T31" s="9" t="n"/>
-      <c r="U31" s="22" t="n"/>
+      <c r="U31" s="9" t="n"/>
+      <c r="V31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n"/>
@@ -3166,7 +3060,8 @@
       <c r="R32" s="13" t="n"/>
       <c r="S32" s="13" t="n"/>
       <c r="T32" s="13" t="n"/>
-      <c r="U32" s="24" t="n"/>
+      <c r="U32" s="13" t="n"/>
+      <c r="V32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n"/>
@@ -3189,7 +3084,8 @@
       <c r="R33" s="9" t="n"/>
       <c r="S33" s="9" t="n"/>
       <c r="T33" s="9" t="n"/>
-      <c r="U33" s="22" t="n"/>
+      <c r="U33" s="9" t="n"/>
+      <c r="V33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n"/>
@@ -3212,7 +3108,8 @@
       <c r="R34" s="13" t="n"/>
       <c r="S34" s="13" t="n"/>
       <c r="T34" s="13" t="n"/>
-      <c r="U34" s="24" t="n"/>
+      <c r="U34" s="13" t="n"/>
+      <c r="V34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n"/>
@@ -3235,7 +3132,8 @@
       <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
-      <c r="U35" s="22" t="n"/>
+      <c r="U35" s="9" t="n"/>
+      <c r="V35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n"/>
@@ -3258,7 +3156,8 @@
       <c r="R36" s="13" t="n"/>
       <c r="S36" s="13" t="n"/>
       <c r="T36" s="13" t="n"/>
-      <c r="U36" s="24" t="n"/>
+      <c r="U36" s="13" t="n"/>
+      <c r="V36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n"/>
@@ -3281,7 +3180,8 @@
       <c r="R37" s="9" t="n"/>
       <c r="S37" s="9" t="n"/>
       <c r="T37" s="9" t="n"/>
-      <c r="U37" s="22" t="n"/>
+      <c r="U37" s="9" t="n"/>
+      <c r="V37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n"/>
@@ -3304,7 +3204,8 @@
       <c r="R38" s="13" t="n"/>
       <c r="S38" s="13" t="n"/>
       <c r="T38" s="13" t="n"/>
-      <c r="U38" s="24" t="n"/>
+      <c r="U38" s="13" t="n"/>
+      <c r="V38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n"/>
@@ -3327,7 +3228,8 @@
       <c r="R39" s="9" t="n"/>
       <c r="S39" s="9" t="n"/>
       <c r="T39" s="9" t="n"/>
-      <c r="U39" s="22" t="n"/>
+      <c r="U39" s="9" t="n"/>
+      <c r="V39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n"/>
@@ -3350,7 +3252,8 @@
       <c r="R40" s="13" t="n"/>
       <c r="S40" s="13" t="n"/>
       <c r="T40" s="13" t="n"/>
-      <c r="U40" s="24" t="n"/>
+      <c r="U40" s="13" t="n"/>
+      <c r="V40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n"/>
@@ -3373,7 +3276,8 @@
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
-      <c r="U41" s="22" t="n"/>
+      <c r="U41" s="9" t="n"/>
+      <c r="V41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n"/>
@@ -3396,7 +3300,8 @@
       <c r="R42" s="13" t="n"/>
       <c r="S42" s="13" t="n"/>
       <c r="T42" s="13" t="n"/>
-      <c r="U42" s="24" t="n"/>
+      <c r="U42" s="13" t="n"/>
+      <c r="V42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n"/>
@@ -3419,7 +3324,8 @@
       <c r="R43" s="9" t="n"/>
       <c r="S43" s="9" t="n"/>
       <c r="T43" s="9" t="n"/>
-      <c r="U43" s="22" t="n"/>
+      <c r="U43" s="9" t="n"/>
+      <c r="V43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n"/>
@@ -3442,7 +3348,8 @@
       <c r="R44" s="13" t="n"/>
       <c r="S44" s="13" t="n"/>
       <c r="T44" s="13" t="n"/>
-      <c r="U44" s="24" t="n"/>
+      <c r="U44" s="13" t="n"/>
+      <c r="V44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n"/>
@@ -3465,7 +3372,8 @@
       <c r="R45" s="9" t="n"/>
       <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
-      <c r="U45" s="22" t="n"/>
+      <c r="U45" s="9" t="n"/>
+      <c r="V45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n"/>
@@ -3488,7 +3396,8 @@
       <c r="R46" s="13" t="n"/>
       <c r="S46" s="13" t="n"/>
       <c r="T46" s="13" t="n"/>
-      <c r="U46" s="24" t="n"/>
+      <c r="U46" s="13" t="n"/>
+      <c r="V46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n"/>
@@ -3511,7 +3420,8 @@
       <c r="R47" s="9" t="n"/>
       <c r="S47" s="9" t="n"/>
       <c r="T47" s="9" t="n"/>
-      <c r="U47" s="22" t="n"/>
+      <c r="U47" s="9" t="n"/>
+      <c r="V47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n"/>
@@ -3534,7 +3444,8 @@
       <c r="R48" s="13" t="n"/>
       <c r="S48" s="13" t="n"/>
       <c r="T48" s="13" t="n"/>
-      <c r="U48" s="24" t="n"/>
+      <c r="U48" s="13" t="n"/>
+      <c r="V48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n"/>
@@ -3557,7 +3468,8 @@
       <c r="R49" s="9" t="n"/>
       <c r="S49" s="9" t="n"/>
       <c r="T49" s="9" t="n"/>
-      <c r="U49" s="22" t="n"/>
+      <c r="U49" s="9" t="n"/>
+      <c r="V49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n"/>
@@ -3580,7 +3492,8 @@
       <c r="R50" s="13" t="n"/>
       <c r="S50" s="13" t="n"/>
       <c r="T50" s="13" t="n"/>
-      <c r="U50" s="24" t="n"/>
+      <c r="U50" s="13" t="n"/>
+      <c r="V50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n"/>
@@ -3603,7 +3516,8 @@
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n"/>
       <c r="T51" s="9" t="n"/>
-      <c r="U51" s="22" t="n"/>
+      <c r="U51" s="9" t="n"/>
+      <c r="V51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n"/>
@@ -3626,7 +3540,8 @@
       <c r="R52" s="13" t="n"/>
       <c r="S52" s="13" t="n"/>
       <c r="T52" s="13" t="n"/>
-      <c r="U52" s="24" t="n"/>
+      <c r="U52" s="13" t="n"/>
+      <c r="V52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n"/>
@@ -3649,7 +3564,8 @@
       <c r="R53" s="9" t="n"/>
       <c r="S53" s="9" t="n"/>
       <c r="T53" s="9" t="n"/>
-      <c r="U53" s="22" t="n"/>
+      <c r="U53" s="9" t="n"/>
+      <c r="V53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n"/>
@@ -3672,7 +3588,8 @@
       <c r="R54" s="13" t="n"/>
       <c r="S54" s="13" t="n"/>
       <c r="T54" s="13" t="n"/>
-      <c r="U54" s="24" t="n"/>
+      <c r="U54" s="13" t="n"/>
+      <c r="V54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n"/>
@@ -3695,7 +3612,8 @@
       <c r="R55" s="9" t="n"/>
       <c r="S55" s="9" t="n"/>
       <c r="T55" s="9" t="n"/>
-      <c r="U55" s="22" t="n"/>
+      <c r="U55" s="9" t="n"/>
+      <c r="V55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n"/>
@@ -3718,7 +3636,8 @@
       <c r="R56" s="13" t="n"/>
       <c r="S56" s="13" t="n"/>
       <c r="T56" s="13" t="n"/>
-      <c r="U56" s="24" t="n"/>
+      <c r="U56" s="13" t="n"/>
+      <c r="V56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n"/>
@@ -3741,14 +3660,15 @@
       <c r="R57" s="9" t="n"/>
       <c r="S57" s="9" t="n"/>
       <c r="T57" s="9" t="n"/>
-      <c r="U57" s="22" t="n"/>
+      <c r="U57" s="9" t="n"/>
+      <c r="V57" s="22" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="S2:U2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:S2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="S5:S28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -627,15 +636,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -649,46 +673,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -699,11 +763,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -718,31 +790,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -751,11 +847,19 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 설계 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -767,11 +871,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ SW (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ SW (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -783,11 +895,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전장 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전장 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -799,11 +919,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -815,11 +943,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 조립 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 조립 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -831,11 +967,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ DRYRUN (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ DRYRUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -847,11 +991,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ AUTORUN (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ AUTORUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -863,11 +1015,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공 입고예정일 (베트남)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공 입고예정일 (베트남)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-07-15
 • 베트남 가공 발주 시 ★입고 완료 예정일★ 기입
@@ -875,37 +1035,62 @@
 📋 운영:
   ▸ 발주 시 예정일 입력
   ▸ 실제 입고일과 비교 → 지연 여부 추적</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공 입고일 (베트남)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공 입고일 (베트남)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 베트남 외주 가공품 실제 입고일
 • 비워두면 진행중 / 입력 시 입고완료</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1230,7 +1415,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="100" t="inlineStr">
+      <c r="A1" s="103" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 베트남 │ 2026</t>
         </is>
@@ -1258,7 +1443,7 @@
       <c r="V1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="101" t="inlineStr">
+      <c r="A2" s="104" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 베트남 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1281,9 +1466,9 @@
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="16" t="n"/>
       <c r="S2" s="17" t="n"/>
-      <c r="T2" s="102" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:47</t>
+      <c r="T2" s="105" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:00</t>
         </is>
       </c>
       <c r="U2" s="16" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -883,6 +901,28 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
+          <t>▣ 설계 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 설계 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 설계 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
           <t>▣ SW (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
@@ -898,7 +938,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ SW — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• SW 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = SW 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -922,7 +984,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전장 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 전장 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 전장 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -946,7 +1030,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 가공 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 가공 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -970,7 +1076,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 조립 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 조립 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 조립 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -994,7 +1122,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="W4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ DRYRUN — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• DRYRUN 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = DRYRUN 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1018,7 +1168,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="Y4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ AUTORUN — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• AUTORUN 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = AUTORUN 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1038,7 +1210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="AA4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1055,7 +1227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="AB4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1074,7 +1246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
+    <comment ref="AC4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1387,7 +1559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1410,12 +1582,19 @@
     <col width="7" customWidth="1" style="55" min="18" max="18"/>
     <col width="7" customWidth="1" style="55" min="19" max="19"/>
     <col width="7" customWidth="1" style="55" min="20" max="20"/>
-    <col width="10" customWidth="1" style="55" min="21" max="21"/>
-    <col width="28" customWidth="1" style="55" min="22" max="22"/>
+    <col width="7" customWidth="1" style="55" min="21" max="21"/>
+    <col width="7" customWidth="1" style="55" min="22" max="22"/>
+    <col width="7" customWidth="1" style="55" min="23" max="23"/>
+    <col width="7" customWidth="1" style="55" min="24" max="24"/>
+    <col width="7" customWidth="1" style="55" min="25" max="25"/>
+    <col width="7" customWidth="1" style="55" min="26" max="26"/>
+    <col width="7" customWidth="1" style="55" min="27" max="27"/>
+    <col width="10" customWidth="1" style="55" min="28" max="28"/>
+    <col width="28" customWidth="1" style="55" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="103" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 베트남 │ 2026</t>
         </is>
@@ -1440,10 +1619,17 @@
       <c r="S1" s="16" t="n"/>
       <c r="T1" s="16" t="n"/>
       <c r="U1" s="16" t="n"/>
-      <c r="V1" s="17" t="n"/>
+      <c r="V1" s="16" t="n"/>
+      <c r="W1" s="16" t="n"/>
+      <c r="X1" s="16" t="n"/>
+      <c r="Y1" s="16" t="n"/>
+      <c r="Z1" s="16" t="n"/>
+      <c r="AA1" s="16" t="n"/>
+      <c r="AB1" s="16" t="n"/>
+      <c r="AC1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="104" t="inlineStr">
+      <c r="A2" s="110" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 베트남 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1465,14 +1651,21 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="16" t="n"/>
-      <c r="S2" s="17" t="n"/>
-      <c r="T2" s="105" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:00</t>
-        </is>
-      </c>
+      <c r="S2" s="16" t="n"/>
+      <c r="T2" s="16" t="n"/>
       <c r="U2" s="16" t="n"/>
-      <c r="V2" s="17" t="n"/>
+      <c r="V2" s="16" t="n"/>
+      <c r="W2" s="16" t="n"/>
+      <c r="X2" s="16" t="n"/>
+      <c r="Y2" s="16" t="n"/>
+      <c r="Z2" s="17" t="n"/>
+      <c r="AA2" s="111" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:35</t>
+        </is>
+      </c>
+      <c r="AB2" s="16" t="n"/>
+      <c r="AC2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1535,52 +1728,87 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1647,56 +1875,91 @@
           <t>설계</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>SW</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="O4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>전장</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="Q4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="S4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t>조립</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="U4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="V4" s="7" t="inlineStr">
         <is>
           <t>DRY
 RUN</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="W4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="X4" s="7" t="inlineStr">
         <is>
           <t>AUTO
 RUN</t>
         </is>
       </c>
-      <c r="S4" s="70" t="inlineStr">
+      <c r="Y4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="Z4" s="70" t="inlineStr">
         <is>
           <t>가공
 예정일</t>
         </is>
       </c>
-      <c r="T4" s="70" t="inlineStr">
+      <c r="AA4" s="70" t="inlineStr">
         <is>
           <t>가공
 입고일</t>
         </is>
       </c>
-      <c r="U4" s="7" t="inlineStr">
+      <c r="AB4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="V4" s="7" t="inlineStr">
+      <c r="AC4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1762,7 +2025,14 @@
       <c r="S5" s="9" t="n"/>
       <c r="T5" s="9" t="n"/>
       <c r="U5" s="9" t="n"/>
-      <c r="V5" s="22" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="9" t="n"/>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="9" t="n"/>
+      <c r="AA5" s="9" t="n"/>
+      <c r="AB5" s="9" t="n"/>
+      <c r="AC5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1824,7 +2094,14 @@
       <c r="S6" s="13" t="n"/>
       <c r="T6" s="13" t="n"/>
       <c r="U6" s="13" t="n"/>
-      <c r="V6" s="24" t="n"/>
+      <c r="V6" s="13" t="n"/>
+      <c r="W6" s="13" t="n"/>
+      <c r="X6" s="13" t="n"/>
+      <c r="Y6" s="13" t="n"/>
+      <c r="Z6" s="13" t="n"/>
+      <c r="AA6" s="13" t="n"/>
+      <c r="AB6" s="13" t="n"/>
+      <c r="AC6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1886,7 +2163,14 @@
       <c r="S7" s="9" t="n"/>
       <c r="T7" s="9" t="n"/>
       <c r="U7" s="9" t="n"/>
-      <c r="V7" s="22" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="9" t="n"/>
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="9" t="n"/>
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="9" t="n"/>
+      <c r="AC7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1948,7 +2232,14 @@
       <c r="S8" s="13" t="n"/>
       <c r="T8" s="13" t="n"/>
       <c r="U8" s="13" t="n"/>
-      <c r="V8" s="24" t="n"/>
+      <c r="V8" s="13" t="n"/>
+      <c r="W8" s="13" t="n"/>
+      <c r="X8" s="13" t="n"/>
+      <c r="Y8" s="13" t="n"/>
+      <c r="Z8" s="13" t="n"/>
+      <c r="AA8" s="13" t="n"/>
+      <c r="AB8" s="13" t="n"/>
+      <c r="AC8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -2010,7 +2301,14 @@
       <c r="S9" s="9" t="n"/>
       <c r="T9" s="9" t="n"/>
       <c r="U9" s="9" t="n"/>
-      <c r="V9" s="22" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="9" t="n"/>
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="9" t="n"/>
+      <c r="AA9" s="9" t="n"/>
+      <c r="AB9" s="9" t="n"/>
+      <c r="AC9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -2072,7 +2370,14 @@
       <c r="S10" s="13" t="n"/>
       <c r="T10" s="13" t="n"/>
       <c r="U10" s="13" t="n"/>
-      <c r="V10" s="24" t="n"/>
+      <c r="V10" s="13" t="n"/>
+      <c r="W10" s="13" t="n"/>
+      <c r="X10" s="13" t="n"/>
+      <c r="Y10" s="13" t="n"/>
+      <c r="Z10" s="13" t="n"/>
+      <c r="AA10" s="13" t="n"/>
+      <c r="AB10" s="13" t="n"/>
+      <c r="AC10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -2134,7 +2439,14 @@
       <c r="S11" s="9" t="n"/>
       <c r="T11" s="9" t="n"/>
       <c r="U11" s="9" t="n"/>
-      <c r="V11" s="22" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="9" t="n"/>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="9" t="n"/>
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="9" t="n"/>
+      <c r="AC11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -2196,7 +2508,14 @@
       <c r="S12" s="13" t="n"/>
       <c r="T12" s="13" t="n"/>
       <c r="U12" s="13" t="n"/>
-      <c r="V12" s="24" t="n"/>
+      <c r="V12" s="13" t="n"/>
+      <c r="W12" s="13" t="n"/>
+      <c r="X12" s="13" t="n"/>
+      <c r="Y12" s="13" t="n"/>
+      <c r="Z12" s="13" t="n"/>
+      <c r="AA12" s="13" t="n"/>
+      <c r="AB12" s="13" t="n"/>
+      <c r="AC12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -2258,7 +2577,14 @@
       <c r="S13" s="9" t="n"/>
       <c r="T13" s="9" t="n"/>
       <c r="U13" s="9" t="n"/>
-      <c r="V13" s="22" t="n"/>
+      <c r="V13" s="9" t="n"/>
+      <c r="W13" s="9" t="n"/>
+      <c r="X13" s="9" t="n"/>
+      <c r="Y13" s="9" t="n"/>
+      <c r="Z13" s="9" t="n"/>
+      <c r="AA13" s="9" t="n"/>
+      <c r="AB13" s="9" t="n"/>
+      <c r="AC13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -2320,7 +2646,14 @@
       <c r="S14" s="13" t="n"/>
       <c r="T14" s="13" t="n"/>
       <c r="U14" s="13" t="n"/>
-      <c r="V14" s="24" t="n"/>
+      <c r="V14" s="13" t="n"/>
+      <c r="W14" s="13" t="n"/>
+      <c r="X14" s="13" t="n"/>
+      <c r="Y14" s="13" t="n"/>
+      <c r="Z14" s="13" t="n"/>
+      <c r="AA14" s="13" t="n"/>
+      <c r="AB14" s="13" t="n"/>
+      <c r="AC14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -2382,7 +2715,14 @@
       <c r="S15" s="9" t="n"/>
       <c r="T15" s="9" t="n"/>
       <c r="U15" s="9" t="n"/>
-      <c r="V15" s="22" t="n"/>
+      <c r="V15" s="9" t="n"/>
+      <c r="W15" s="9" t="n"/>
+      <c r="X15" s="9" t="n"/>
+      <c r="Y15" s="9" t="n"/>
+      <c r="Z15" s="9" t="n"/>
+      <c r="AA15" s="9" t="n"/>
+      <c r="AB15" s="9" t="n"/>
+      <c r="AC15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -2444,7 +2784,14 @@
       <c r="S16" s="13" t="n"/>
       <c r="T16" s="13" t="n"/>
       <c r="U16" s="13" t="n"/>
-      <c r="V16" s="24" t="n"/>
+      <c r="V16" s="13" t="n"/>
+      <c r="W16" s="13" t="n"/>
+      <c r="X16" s="13" t="n"/>
+      <c r="Y16" s="13" t="n"/>
+      <c r="Z16" s="13" t="n"/>
+      <c r="AA16" s="13" t="n"/>
+      <c r="AB16" s="13" t="n"/>
+      <c r="AC16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -2506,7 +2853,14 @@
       <c r="S17" s="9" t="n"/>
       <c r="T17" s="9" t="n"/>
       <c r="U17" s="9" t="n"/>
-      <c r="V17" s="22" t="n"/>
+      <c r="V17" s="9" t="n"/>
+      <c r="W17" s="9" t="n"/>
+      <c r="X17" s="9" t="n"/>
+      <c r="Y17" s="9" t="n"/>
+      <c r="Z17" s="9" t="n"/>
+      <c r="AA17" s="9" t="n"/>
+      <c r="AB17" s="9" t="n"/>
+      <c r="AC17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -2568,7 +2922,14 @@
       <c r="S18" s="13" t="n"/>
       <c r="T18" s="13" t="n"/>
       <c r="U18" s="13" t="n"/>
-      <c r="V18" s="24" t="n"/>
+      <c r="V18" s="13" t="n"/>
+      <c r="W18" s="13" t="n"/>
+      <c r="X18" s="13" t="n"/>
+      <c r="Y18" s="13" t="n"/>
+      <c r="Z18" s="13" t="n"/>
+      <c r="AA18" s="13" t="n"/>
+      <c r="AB18" s="13" t="n"/>
+      <c r="AC18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2630,7 +2991,14 @@
       <c r="S19" s="9" t="n"/>
       <c r="T19" s="9" t="n"/>
       <c r="U19" s="9" t="n"/>
-      <c r="V19" s="22" t="n"/>
+      <c r="V19" s="9" t="n"/>
+      <c r="W19" s="9" t="n"/>
+      <c r="X19" s="9" t="n"/>
+      <c r="Y19" s="9" t="n"/>
+      <c r="Z19" s="9" t="n"/>
+      <c r="AA19" s="9" t="n"/>
+      <c r="AB19" s="9" t="n"/>
+      <c r="AC19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2692,7 +3060,14 @@
       <c r="S20" s="13" t="n"/>
       <c r="T20" s="13" t="n"/>
       <c r="U20" s="13" t="n"/>
-      <c r="V20" s="24" t="n"/>
+      <c r="V20" s="13" t="n"/>
+      <c r="W20" s="13" t="n"/>
+      <c r="X20" s="13" t="n"/>
+      <c r="Y20" s="13" t="n"/>
+      <c r="Z20" s="13" t="n"/>
+      <c r="AA20" s="13" t="n"/>
+      <c r="AB20" s="13" t="n"/>
+      <c r="AC20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2754,7 +3129,14 @@
       <c r="S21" s="9" t="n"/>
       <c r="T21" s="9" t="n"/>
       <c r="U21" s="9" t="n"/>
-      <c r="V21" s="22" t="n"/>
+      <c r="V21" s="9" t="n"/>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="9" t="n"/>
+      <c r="Y21" s="9" t="n"/>
+      <c r="Z21" s="9" t="n"/>
+      <c r="AA21" s="9" t="n"/>
+      <c r="AB21" s="9" t="n"/>
+      <c r="AC21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2816,7 +3198,14 @@
       <c r="S22" s="13" t="n"/>
       <c r="T22" s="13" t="n"/>
       <c r="U22" s="13" t="n"/>
-      <c r="V22" s="24" t="n"/>
+      <c r="V22" s="13" t="n"/>
+      <c r="W22" s="13" t="n"/>
+      <c r="X22" s="13" t="n"/>
+      <c r="Y22" s="13" t="n"/>
+      <c r="Z22" s="13" t="n"/>
+      <c r="AA22" s="13" t="n"/>
+      <c r="AB22" s="13" t="n"/>
+      <c r="AC22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2878,7 +3267,14 @@
       <c r="S23" s="9" t="n"/>
       <c r="T23" s="9" t="n"/>
       <c r="U23" s="9" t="n"/>
-      <c r="V23" s="22" t="n"/>
+      <c r="V23" s="9" t="n"/>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="9" t="n"/>
+      <c r="Y23" s="9" t="n"/>
+      <c r="Z23" s="9" t="n"/>
+      <c r="AA23" s="9" t="n"/>
+      <c r="AB23" s="9" t="n"/>
+      <c r="AC23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2940,7 +3336,14 @@
       <c r="S24" s="13" t="n"/>
       <c r="T24" s="13" t="n"/>
       <c r="U24" s="13" t="n"/>
-      <c r="V24" s="24" t="n"/>
+      <c r="V24" s="13" t="n"/>
+      <c r="W24" s="13" t="n"/>
+      <c r="X24" s="13" t="n"/>
+      <c r="Y24" s="13" t="n"/>
+      <c r="Z24" s="13" t="n"/>
+      <c r="AA24" s="13" t="n"/>
+      <c r="AB24" s="13" t="n"/>
+      <c r="AC24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -3002,7 +3405,14 @@
       <c r="S25" s="9" t="n"/>
       <c r="T25" s="9" t="n"/>
       <c r="U25" s="9" t="n"/>
-      <c r="V25" s="22" t="n"/>
+      <c r="V25" s="9" t="n"/>
+      <c r="W25" s="9" t="n"/>
+      <c r="X25" s="9" t="n"/>
+      <c r="Y25" s="9" t="n"/>
+      <c r="Z25" s="9" t="n"/>
+      <c r="AA25" s="9" t="n"/>
+      <c r="AB25" s="9" t="n"/>
+      <c r="AC25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -3064,7 +3474,14 @@
       <c r="S26" s="13" t="n"/>
       <c r="T26" s="13" t="n"/>
       <c r="U26" s="13" t="n"/>
-      <c r="V26" s="24" t="n"/>
+      <c r="V26" s="13" t="n"/>
+      <c r="W26" s="13" t="n"/>
+      <c r="X26" s="13" t="n"/>
+      <c r="Y26" s="13" t="n"/>
+      <c r="Z26" s="13" t="n"/>
+      <c r="AA26" s="13" t="n"/>
+      <c r="AB26" s="13" t="n"/>
+      <c r="AC26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -3126,7 +3543,14 @@
       <c r="S27" s="9" t="n"/>
       <c r="T27" s="9" t="n"/>
       <c r="U27" s="9" t="n"/>
-      <c r="V27" s="22" t="n"/>
+      <c r="V27" s="9" t="n"/>
+      <c r="W27" s="9" t="n"/>
+      <c r="X27" s="9" t="n"/>
+      <c r="Y27" s="9" t="n"/>
+      <c r="Z27" s="9" t="n"/>
+      <c r="AA27" s="9" t="n"/>
+      <c r="AB27" s="9" t="n"/>
+      <c r="AC27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n"/>
@@ -3150,7 +3574,14 @@
       <c r="S28" s="13" t="n"/>
       <c r="T28" s="13" t="n"/>
       <c r="U28" s="13" t="n"/>
-      <c r="V28" s="24" t="n"/>
+      <c r="V28" s="13" t="n"/>
+      <c r="W28" s="13" t="n"/>
+      <c r="X28" s="13" t="n"/>
+      <c r="Y28" s="13" t="n"/>
+      <c r="Z28" s="13" t="n"/>
+      <c r="AA28" s="13" t="n"/>
+      <c r="AB28" s="13" t="n"/>
+      <c r="AC28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n"/>
@@ -3174,7 +3605,14 @@
       <c r="S29" s="9" t="n"/>
       <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
-      <c r="V29" s="22" t="n"/>
+      <c r="V29" s="9" t="n"/>
+      <c r="W29" s="9" t="n"/>
+      <c r="X29" s="9" t="n"/>
+      <c r="Y29" s="9" t="n"/>
+      <c r="Z29" s="9" t="n"/>
+      <c r="AA29" s="9" t="n"/>
+      <c r="AB29" s="9" t="n"/>
+      <c r="AC29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n"/>
@@ -3198,7 +3636,14 @@
       <c r="S30" s="13" t="n"/>
       <c r="T30" s="13" t="n"/>
       <c r="U30" s="13" t="n"/>
-      <c r="V30" s="24" t="n"/>
+      <c r="V30" s="13" t="n"/>
+      <c r="W30" s="13" t="n"/>
+      <c r="X30" s="13" t="n"/>
+      <c r="Y30" s="13" t="n"/>
+      <c r="Z30" s="13" t="n"/>
+      <c r="AA30" s="13" t="n"/>
+      <c r="AB30" s="13" t="n"/>
+      <c r="AC30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n"/>
@@ -3222,7 +3667,14 @@
       <c r="S31" s="9" t="n"/>
       <c r="T31" s="9" t="n"/>
       <c r="U31" s="9" t="n"/>
-      <c r="V31" s="22" t="n"/>
+      <c r="V31" s="9" t="n"/>
+      <c r="W31" s="9" t="n"/>
+      <c r="X31" s="9" t="n"/>
+      <c r="Y31" s="9" t="n"/>
+      <c r="Z31" s="9" t="n"/>
+      <c r="AA31" s="9" t="n"/>
+      <c r="AB31" s="9" t="n"/>
+      <c r="AC31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n"/>
@@ -3246,7 +3698,14 @@
       <c r="S32" s="13" t="n"/>
       <c r="T32" s="13" t="n"/>
       <c r="U32" s="13" t="n"/>
-      <c r="V32" s="24" t="n"/>
+      <c r="V32" s="13" t="n"/>
+      <c r="W32" s="13" t="n"/>
+      <c r="X32" s="13" t="n"/>
+      <c r="Y32" s="13" t="n"/>
+      <c r="Z32" s="13" t="n"/>
+      <c r="AA32" s="13" t="n"/>
+      <c r="AB32" s="13" t="n"/>
+      <c r="AC32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n"/>
@@ -3270,7 +3729,14 @@
       <c r="S33" s="9" t="n"/>
       <c r="T33" s="9" t="n"/>
       <c r="U33" s="9" t="n"/>
-      <c r="V33" s="22" t="n"/>
+      <c r="V33" s="9" t="n"/>
+      <c r="W33" s="9" t="n"/>
+      <c r="X33" s="9" t="n"/>
+      <c r="Y33" s="9" t="n"/>
+      <c r="Z33" s="9" t="n"/>
+      <c r="AA33" s="9" t="n"/>
+      <c r="AB33" s="9" t="n"/>
+      <c r="AC33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n"/>
@@ -3294,7 +3760,14 @@
       <c r="S34" s="13" t="n"/>
       <c r="T34" s="13" t="n"/>
       <c r="U34" s="13" t="n"/>
-      <c r="V34" s="24" t="n"/>
+      <c r="V34" s="13" t="n"/>
+      <c r="W34" s="13" t="n"/>
+      <c r="X34" s="13" t="n"/>
+      <c r="Y34" s="13" t="n"/>
+      <c r="Z34" s="13" t="n"/>
+      <c r="AA34" s="13" t="n"/>
+      <c r="AB34" s="13" t="n"/>
+      <c r="AC34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n"/>
@@ -3318,7 +3791,14 @@
       <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
-      <c r="V35" s="22" t="n"/>
+      <c r="V35" s="9" t="n"/>
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="9" t="n"/>
+      <c r="Y35" s="9" t="n"/>
+      <c r="Z35" s="9" t="n"/>
+      <c r="AA35" s="9" t="n"/>
+      <c r="AB35" s="9" t="n"/>
+      <c r="AC35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n"/>
@@ -3342,7 +3822,14 @@
       <c r="S36" s="13" t="n"/>
       <c r="T36" s="13" t="n"/>
       <c r="U36" s="13" t="n"/>
-      <c r="V36" s="24" t="n"/>
+      <c r="V36" s="13" t="n"/>
+      <c r="W36" s="13" t="n"/>
+      <c r="X36" s="13" t="n"/>
+      <c r="Y36" s="13" t="n"/>
+      <c r="Z36" s="13" t="n"/>
+      <c r="AA36" s="13" t="n"/>
+      <c r="AB36" s="13" t="n"/>
+      <c r="AC36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n"/>
@@ -3366,7 +3853,14 @@
       <c r="S37" s="9" t="n"/>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="9" t="n"/>
-      <c r="V37" s="22" t="n"/>
+      <c r="V37" s="9" t="n"/>
+      <c r="W37" s="9" t="n"/>
+      <c r="X37" s="9" t="n"/>
+      <c r="Y37" s="9" t="n"/>
+      <c r="Z37" s="9" t="n"/>
+      <c r="AA37" s="9" t="n"/>
+      <c r="AB37" s="9" t="n"/>
+      <c r="AC37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n"/>
@@ -3390,7 +3884,14 @@
       <c r="S38" s="13" t="n"/>
       <c r="T38" s="13" t="n"/>
       <c r="U38" s="13" t="n"/>
-      <c r="V38" s="24" t="n"/>
+      <c r="V38" s="13" t="n"/>
+      <c r="W38" s="13" t="n"/>
+      <c r="X38" s="13" t="n"/>
+      <c r="Y38" s="13" t="n"/>
+      <c r="Z38" s="13" t="n"/>
+      <c r="AA38" s="13" t="n"/>
+      <c r="AB38" s="13" t="n"/>
+      <c r="AC38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n"/>
@@ -3414,7 +3915,14 @@
       <c r="S39" s="9" t="n"/>
       <c r="T39" s="9" t="n"/>
       <c r="U39" s="9" t="n"/>
-      <c r="V39" s="22" t="n"/>
+      <c r="V39" s="9" t="n"/>
+      <c r="W39" s="9" t="n"/>
+      <c r="X39" s="9" t="n"/>
+      <c r="Y39" s="9" t="n"/>
+      <c r="Z39" s="9" t="n"/>
+      <c r="AA39" s="9" t="n"/>
+      <c r="AB39" s="9" t="n"/>
+      <c r="AC39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n"/>
@@ -3438,7 +3946,14 @@
       <c r="S40" s="13" t="n"/>
       <c r="T40" s="13" t="n"/>
       <c r="U40" s="13" t="n"/>
-      <c r="V40" s="24" t="n"/>
+      <c r="V40" s="13" t="n"/>
+      <c r="W40" s="13" t="n"/>
+      <c r="X40" s="13" t="n"/>
+      <c r="Y40" s="13" t="n"/>
+      <c r="Z40" s="13" t="n"/>
+      <c r="AA40" s="13" t="n"/>
+      <c r="AB40" s="13" t="n"/>
+      <c r="AC40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n"/>
@@ -3462,7 +3977,14 @@
       <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="9" t="n"/>
-      <c r="V41" s="22" t="n"/>
+      <c r="V41" s="9" t="n"/>
+      <c r="W41" s="9" t="n"/>
+      <c r="X41" s="9" t="n"/>
+      <c r="Y41" s="9" t="n"/>
+      <c r="Z41" s="9" t="n"/>
+      <c r="AA41" s="9" t="n"/>
+      <c r="AB41" s="9" t="n"/>
+      <c r="AC41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n"/>
@@ -3486,7 +4008,14 @@
       <c r="S42" s="13" t="n"/>
       <c r="T42" s="13" t="n"/>
       <c r="U42" s="13" t="n"/>
-      <c r="V42" s="24" t="n"/>
+      <c r="V42" s="13" t="n"/>
+      <c r="W42" s="13" t="n"/>
+      <c r="X42" s="13" t="n"/>
+      <c r="Y42" s="13" t="n"/>
+      <c r="Z42" s="13" t="n"/>
+      <c r="AA42" s="13" t="n"/>
+      <c r="AB42" s="13" t="n"/>
+      <c r="AC42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n"/>
@@ -3510,7 +4039,14 @@
       <c r="S43" s="9" t="n"/>
       <c r="T43" s="9" t="n"/>
       <c r="U43" s="9" t="n"/>
-      <c r="V43" s="22" t="n"/>
+      <c r="V43" s="9" t="n"/>
+      <c r="W43" s="9" t="n"/>
+      <c r="X43" s="9" t="n"/>
+      <c r="Y43" s="9" t="n"/>
+      <c r="Z43" s="9" t="n"/>
+      <c r="AA43" s="9" t="n"/>
+      <c r="AB43" s="9" t="n"/>
+      <c r="AC43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n"/>
@@ -3534,7 +4070,14 @@
       <c r="S44" s="13" t="n"/>
       <c r="T44" s="13" t="n"/>
       <c r="U44" s="13" t="n"/>
-      <c r="V44" s="24" t="n"/>
+      <c r="V44" s="13" t="n"/>
+      <c r="W44" s="13" t="n"/>
+      <c r="X44" s="13" t="n"/>
+      <c r="Y44" s="13" t="n"/>
+      <c r="Z44" s="13" t="n"/>
+      <c r="AA44" s="13" t="n"/>
+      <c r="AB44" s="13" t="n"/>
+      <c r="AC44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n"/>
@@ -3558,7 +4101,14 @@
       <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="9" t="n"/>
-      <c r="V45" s="22" t="n"/>
+      <c r="V45" s="9" t="n"/>
+      <c r="W45" s="9" t="n"/>
+      <c r="X45" s="9" t="n"/>
+      <c r="Y45" s="9" t="n"/>
+      <c r="Z45" s="9" t="n"/>
+      <c r="AA45" s="9" t="n"/>
+      <c r="AB45" s="9" t="n"/>
+      <c r="AC45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n"/>
@@ -3582,7 +4132,14 @@
       <c r="S46" s="13" t="n"/>
       <c r="T46" s="13" t="n"/>
       <c r="U46" s="13" t="n"/>
-      <c r="V46" s="24" t="n"/>
+      <c r="V46" s="13" t="n"/>
+      <c r="W46" s="13" t="n"/>
+      <c r="X46" s="13" t="n"/>
+      <c r="Y46" s="13" t="n"/>
+      <c r="Z46" s="13" t="n"/>
+      <c r="AA46" s="13" t="n"/>
+      <c r="AB46" s="13" t="n"/>
+      <c r="AC46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n"/>
@@ -3606,7 +4163,14 @@
       <c r="S47" s="9" t="n"/>
       <c r="T47" s="9" t="n"/>
       <c r="U47" s="9" t="n"/>
-      <c r="V47" s="22" t="n"/>
+      <c r="V47" s="9" t="n"/>
+      <c r="W47" s="9" t="n"/>
+      <c r="X47" s="9" t="n"/>
+      <c r="Y47" s="9" t="n"/>
+      <c r="Z47" s="9" t="n"/>
+      <c r="AA47" s="9" t="n"/>
+      <c r="AB47" s="9" t="n"/>
+      <c r="AC47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n"/>
@@ -3630,7 +4194,14 @@
       <c r="S48" s="13" t="n"/>
       <c r="T48" s="13" t="n"/>
       <c r="U48" s="13" t="n"/>
-      <c r="V48" s="24" t="n"/>
+      <c r="V48" s="13" t="n"/>
+      <c r="W48" s="13" t="n"/>
+      <c r="X48" s="13" t="n"/>
+      <c r="Y48" s="13" t="n"/>
+      <c r="Z48" s="13" t="n"/>
+      <c r="AA48" s="13" t="n"/>
+      <c r="AB48" s="13" t="n"/>
+      <c r="AC48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n"/>
@@ -3654,7 +4225,14 @@
       <c r="S49" s="9" t="n"/>
       <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
-      <c r="V49" s="22" t="n"/>
+      <c r="V49" s="9" t="n"/>
+      <c r="W49" s="9" t="n"/>
+      <c r="X49" s="9" t="n"/>
+      <c r="Y49" s="9" t="n"/>
+      <c r="Z49" s="9" t="n"/>
+      <c r="AA49" s="9" t="n"/>
+      <c r="AB49" s="9" t="n"/>
+      <c r="AC49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n"/>
@@ -3678,7 +4256,14 @@
       <c r="S50" s="13" t="n"/>
       <c r="T50" s="13" t="n"/>
       <c r="U50" s="13" t="n"/>
-      <c r="V50" s="24" t="n"/>
+      <c r="V50" s="13" t="n"/>
+      <c r="W50" s="13" t="n"/>
+      <c r="X50" s="13" t="n"/>
+      <c r="Y50" s="13" t="n"/>
+      <c r="Z50" s="13" t="n"/>
+      <c r="AA50" s="13" t="n"/>
+      <c r="AB50" s="13" t="n"/>
+      <c r="AC50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n"/>
@@ -3702,7 +4287,14 @@
       <c r="S51" s="9" t="n"/>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
-      <c r="V51" s="22" t="n"/>
+      <c r="V51" s="9" t="n"/>
+      <c r="W51" s="9" t="n"/>
+      <c r="X51" s="9" t="n"/>
+      <c r="Y51" s="9" t="n"/>
+      <c r="Z51" s="9" t="n"/>
+      <c r="AA51" s="9" t="n"/>
+      <c r="AB51" s="9" t="n"/>
+      <c r="AC51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n"/>
@@ -3726,7 +4318,14 @@
       <c r="S52" s="13" t="n"/>
       <c r="T52" s="13" t="n"/>
       <c r="U52" s="13" t="n"/>
-      <c r="V52" s="24" t="n"/>
+      <c r="V52" s="13" t="n"/>
+      <c r="W52" s="13" t="n"/>
+      <c r="X52" s="13" t="n"/>
+      <c r="Y52" s="13" t="n"/>
+      <c r="Z52" s="13" t="n"/>
+      <c r="AA52" s="13" t="n"/>
+      <c r="AB52" s="13" t="n"/>
+      <c r="AC52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n"/>
@@ -3750,7 +4349,14 @@
       <c r="S53" s="9" t="n"/>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
-      <c r="V53" s="22" t="n"/>
+      <c r="V53" s="9" t="n"/>
+      <c r="W53" s="9" t="n"/>
+      <c r="X53" s="9" t="n"/>
+      <c r="Y53" s="9" t="n"/>
+      <c r="Z53" s="9" t="n"/>
+      <c r="AA53" s="9" t="n"/>
+      <c r="AB53" s="9" t="n"/>
+      <c r="AC53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n"/>
@@ -3774,7 +4380,14 @@
       <c r="S54" s="13" t="n"/>
       <c r="T54" s="13" t="n"/>
       <c r="U54" s="13" t="n"/>
-      <c r="V54" s="24" t="n"/>
+      <c r="V54" s="13" t="n"/>
+      <c r="W54" s="13" t="n"/>
+      <c r="X54" s="13" t="n"/>
+      <c r="Y54" s="13" t="n"/>
+      <c r="Z54" s="13" t="n"/>
+      <c r="AA54" s="13" t="n"/>
+      <c r="AB54" s="13" t="n"/>
+      <c r="AC54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n"/>
@@ -3798,7 +4411,14 @@
       <c r="S55" s="9" t="n"/>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
-      <c r="V55" s="22" t="n"/>
+      <c r="V55" s="9" t="n"/>
+      <c r="W55" s="9" t="n"/>
+      <c r="X55" s="9" t="n"/>
+      <c r="Y55" s="9" t="n"/>
+      <c r="Z55" s="9" t="n"/>
+      <c r="AA55" s="9" t="n"/>
+      <c r="AB55" s="9" t="n"/>
+      <c r="AC55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n"/>
@@ -3822,7 +4442,14 @@
       <c r="S56" s="13" t="n"/>
       <c r="T56" s="13" t="n"/>
       <c r="U56" s="13" t="n"/>
-      <c r="V56" s="24" t="n"/>
+      <c r="V56" s="13" t="n"/>
+      <c r="W56" s="13" t="n"/>
+      <c r="X56" s="13" t="n"/>
+      <c r="Y56" s="13" t="n"/>
+      <c r="Z56" s="13" t="n"/>
+      <c r="AA56" s="13" t="n"/>
+      <c r="AB56" s="13" t="n"/>
+      <c r="AC56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n"/>
@@ -3846,14 +4473,21 @@
       <c r="S57" s="9" t="n"/>
       <c r="T57" s="9" t="n"/>
       <c r="U57" s="9" t="n"/>
-      <c r="V57" s="22" t="n"/>
+      <c r="V57" s="9" t="n"/>
+      <c r="W57" s="9" t="n"/>
+      <c r="X57" s="9" t="n"/>
+      <c r="Y57" s="9" t="n"/>
+      <c r="Z57" s="9" t="n"/>
+      <c r="AA57" s="9" t="n"/>
+      <c r="AB57" s="9" t="n"/>
+      <c r="AC57" s="22" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="3">
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="A1:AC1"/>
+    <mergeCell ref="A2:Z2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="S5:S28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -66,7 +66,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +121,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00B08F36"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000277BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF6C00"/>
       </patternFill>
     </fill>
   </fills>
@@ -237,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -569,6 +579,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1594,7 +1619,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="109" t="inlineStr">
+      <c r="A1" s="112" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 베트남 │ 2026</t>
         </is>
@@ -1629,7 +1654,7 @@
       <c r="AC1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="113" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 베트남 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1659,9 +1684,9 @@
       <c r="X2" s="16" t="n"/>
       <c r="Y2" s="16" t="n"/>
       <c r="Z2" s="17" t="n"/>
-      <c r="AA2" s="111" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:35</t>
+      <c r="AA2" s="114" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 15:15</t>
         </is>
       </c>
       <c r="AB2" s="16" t="n"/>
@@ -1870,74 +1895,74 @@
           <t>부서진척률(%)</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="115" t="inlineStr">
         <is>
           <t>설계</t>
         </is>
       </c>
-      <c r="M4" s="70" t="inlineStr">
+      <c r="M4" s="115" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="116" t="inlineStr">
         <is>
           <t>SW</t>
         </is>
       </c>
-      <c r="O4" s="70" t="inlineStr">
+      <c r="O4" s="116" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="P4" s="115" t="inlineStr">
         <is>
           <t>전장</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="inlineStr">
+      <c r="Q4" s="115" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="R4" s="116" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="S4" s="70" t="inlineStr">
+      <c r="S4" s="116" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="T4" s="7" t="inlineStr">
+      <c r="T4" s="115" t="inlineStr">
         <is>
           <t>조립</t>
         </is>
       </c>
-      <c r="U4" s="70" t="inlineStr">
+      <c r="U4" s="115" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="V4" s="7" t="inlineStr">
+      <c r="V4" s="116" t="inlineStr">
         <is>
           <t>DRY
 RUN</t>
         </is>
       </c>
-      <c r="W4" s="70" t="inlineStr">
+      <c r="W4" s="116" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="X4" s="7" t="inlineStr">
+      <c r="X4" s="115" t="inlineStr">
         <is>
           <t>AUTO
 RUN</t>
         </is>
       </c>
-      <c r="Y4" s="70" t="inlineStr">
+      <c r="Y4" s="115" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
